--- a/adj mat/awake_FCPreProc.xlsx
+++ b/adj mat/awake_FCPreProc.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="12242" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="20107" uniqueCount="408">
   <si>
     <t>path</t>
   </si>
@@ -736,6 +736,507 @@
   </si>
   <si>
     <t>folder</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/networks-pm/replica/pm/derivatives/FCProc-24.1.1/sub-1/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/networks-pm/replica/pm/derivatives/FCProc-24.1.1/sub-1/ses-5/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/networks-pm/replica/pm/derivatives/FCProc-24.1.1/sub-1/ses-7/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/networks-pm/replica/pm/derivatives/FCProc-24.1.1/sub-1/ses-11/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/networks-pm/replica/pm/derivatives/FCProc-24.1.1/sub-1/ses-14/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/networks-pm/replica/pm/derivatives/FCProc-24.1.1/sub-1/ses-17/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/networks-pm/replica/pm/derivatives/FCProc-24.1.1/sub-1/ses-18/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/networks-pm/replica/pm/derivatives/FCProc-24.1.1/sub-1/ses-20/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET001/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET001/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET001/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET001/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET001/ses-5/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET002/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET002/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET002/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET003/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET003/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET010/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET010/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET019/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET019/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET019/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET032/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET032/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET035/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET035/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET035/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET039/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET039/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET039/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET039/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET040/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET040/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET040/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET044/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET044/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET044/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET044/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET045/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET045/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET045/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET045/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET047/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET047/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET049/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET049/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET050/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET050/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET050/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET050/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET051/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET051/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET051/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET051/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET053/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET053/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET055/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET055/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET057/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET057/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET057/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET058/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET063/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET065/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET065/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET065/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET067/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET067/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET068/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET070/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET070/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET070/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET070/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET077/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET077/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET077/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET083/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET083/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET084/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET084/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET085/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET085/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET085/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET086/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET086/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET088/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET088/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET091/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET093/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET093/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET093/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET093/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET094/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET094/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET096/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET096/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET096/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET098/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET098/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET098/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET099/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET099/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET099/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET101/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET101/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET101/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET101/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET103/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET103/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET103/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET103/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET104/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET104/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET104/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET106/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET106/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET107/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET108/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET108/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET109/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET109/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET110/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET110/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET120/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET123/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET123/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET123/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET131/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET131/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET133/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET133/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET133/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET133/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET136/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET136/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET136/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET136/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET137/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET137/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET140/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET140/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET141/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET141/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET141/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET156/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET156/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET156/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET158/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET159/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET159/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET159/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET159/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET168/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET168/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET168/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET168/ses-4/func/</t>
   </si>
 </sst>
 </file>
@@ -786,7 +1287,7 @@
   <cols>
     <col min="1" max="1" width="8.140625" customWidth="true"/>
     <col min="2" max="2" width="7.7109375" customWidth="true"/>
-    <col min="3" max="3" width="99.140625" customWidth="true"/>
+    <col min="3" max="3" width="101.5703125" customWidth="true"/>
     <col min="4" max="4" width="7.28515625" customWidth="true"/>
     <col min="5" max="5" width="4.140625" customWidth="true"/>
   </cols>
@@ -812,11 +1313,11 @@
       <c r="A2" s="0" t="s">
         <v>179</v>
       </c>
-      <c r="B2" s="0">
-        <v>1</v>
+      <c r="B2" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>1</v>
+        <v>251</v>
       </c>
       <c r="D2" s="0" t="s">
         <v>237</v>
@@ -827,11 +1328,11 @@
       <c r="A3" s="0" t="s">
         <v>179</v>
       </c>
-      <c r="B3" s="0">
-        <v>5</v>
+      <c r="B3" s="0" t="s">
+        <v>241</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="D3" s="0" t="s">
         <v>237</v>
@@ -842,11 +1343,11 @@
       <c r="A4" s="0" t="s">
         <v>179</v>
       </c>
-      <c r="B4" s="0">
-        <v>7</v>
+      <c r="B4" s="0" t="s">
+        <v>242</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>1</v>
+        <v>253</v>
       </c>
       <c r="D4" s="0" t="s">
         <v>237</v>
@@ -857,11 +1358,11 @@
       <c r="A5" s="0" t="s">
         <v>179</v>
       </c>
-      <c r="B5" s="0">
-        <v>11</v>
+      <c r="B5" s="0" t="s">
+        <v>243</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>1</v>
+        <v>254</v>
       </c>
       <c r="D5" s="0" t="s">
         <v>237</v>
@@ -872,11 +1373,11 @@
       <c r="A6" s="0" t="s">
         <v>179</v>
       </c>
-      <c r="B6" s="0">
-        <v>14</v>
+      <c r="B6" s="0" t="s">
+        <v>244</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>1</v>
+        <v>255</v>
       </c>
       <c r="D6" s="0" t="s">
         <v>237</v>
@@ -887,11 +1388,11 @@
       <c r="A7" s="0" t="s">
         <v>179</v>
       </c>
-      <c r="B7" s="0">
-        <v>17</v>
+      <c r="B7" s="0" t="s">
+        <v>245</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>1</v>
+        <v>256</v>
       </c>
       <c r="D7" s="0" t="s">
         <v>237</v>
@@ -902,11 +1403,11 @@
       <c r="A8" s="0" t="s">
         <v>179</v>
       </c>
-      <c r="B8" s="0">
-        <v>18</v>
+      <c r="B8" s="0" t="s">
+        <v>246</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="D8" s="0" t="s">
         <v>237</v>
@@ -917,11 +1418,11 @@
       <c r="A9" s="0" t="s">
         <v>179</v>
       </c>
-      <c r="B9" s="0">
-        <v>20</v>
+      <c r="B9" s="0" t="s">
+        <v>247</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>1</v>
+        <v>258</v>
       </c>
       <c r="D9" s="0" t="s">
         <v>237</v>
@@ -932,11 +1433,11 @@
       <c r="A10" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B10" s="0">
-        <v>1</v>
+      <c r="B10" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>1</v>
+        <v>259</v>
       </c>
       <c r="D10" s="0" t="s">
         <v>237</v>
@@ -949,11 +1450,11 @@
       <c r="A11" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B11" s="0">
-        <v>1</v>
+      <c r="B11" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>1</v>
+        <v>259</v>
       </c>
       <c r="D11" s="0" t="s">
         <v>237</v>
@@ -966,11 +1467,11 @@
       <c r="A12" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B12" s="0">
-        <v>1</v>
+      <c r="B12" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>1</v>
+        <v>259</v>
       </c>
       <c r="D12" s="0" t="s">
         <v>237</v>
@@ -983,11 +1484,11 @@
       <c r="A13" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B13" s="0">
-        <v>1</v>
+      <c r="B13" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>1</v>
+        <v>259</v>
       </c>
       <c r="D13" s="0" t="s">
         <v>237</v>
@@ -1000,11 +1501,11 @@
       <c r="A14" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B14" s="0">
-        <v>1</v>
+      <c r="B14" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>1</v>
+        <v>259</v>
       </c>
       <c r="D14" s="0" t="s">
         <v>237</v>
@@ -1017,11 +1518,11 @@
       <c r="A15" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B15" s="0">
-        <v>1</v>
+      <c r="B15" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>1</v>
+        <v>259</v>
       </c>
       <c r="D15" s="0" t="s">
         <v>237</v>
@@ -1034,11 +1535,11 @@
       <c r="A16" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B16" s="0">
-        <v>2</v>
+      <c r="B16" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>1</v>
+        <v>260</v>
       </c>
       <c r="D16" s="0" t="s">
         <v>237</v>
@@ -1051,11 +1552,11 @@
       <c r="A17" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B17" s="0">
-        <v>2</v>
+      <c r="B17" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>1</v>
+        <v>260</v>
       </c>
       <c r="D17" s="0" t="s">
         <v>237</v>
@@ -1068,11 +1569,11 @@
       <c r="A18" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B18" s="0">
-        <v>2</v>
+      <c r="B18" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>1</v>
+        <v>260</v>
       </c>
       <c r="D18" s="0" t="s">
         <v>237</v>
@@ -1085,11 +1586,11 @@
       <c r="A19" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B19" s="0">
-        <v>2</v>
+      <c r="B19" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>1</v>
+        <v>260</v>
       </c>
       <c r="D19" s="0" t="s">
         <v>237</v>
@@ -1102,11 +1603,11 @@
       <c r="A20" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B20" s="0">
-        <v>2</v>
+      <c r="B20" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>1</v>
+        <v>260</v>
       </c>
       <c r="D20" s="0" t="s">
         <v>237</v>
@@ -1119,11 +1620,11 @@
       <c r="A21" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B21" s="0">
-        <v>2</v>
+      <c r="B21" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>1</v>
+        <v>260</v>
       </c>
       <c r="D21" s="0" t="s">
         <v>237</v>
@@ -1136,11 +1637,11 @@
       <c r="A22" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B22" s="0">
-        <v>2</v>
+      <c r="B22" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>1</v>
+        <v>260</v>
       </c>
       <c r="D22" s="0" t="s">
         <v>237</v>
@@ -1153,11 +1654,11 @@
       <c r="A23" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B23" s="0">
-        <v>3</v>
+      <c r="B23" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>1</v>
+        <v>261</v>
       </c>
       <c r="D23" s="0" t="s">
         <v>237</v>
@@ -1170,11 +1671,11 @@
       <c r="A24" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B24" s="0">
-        <v>3</v>
+      <c r="B24" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>1</v>
+        <v>261</v>
       </c>
       <c r="D24" s="0" t="s">
         <v>237</v>
@@ -1187,11 +1688,11 @@
       <c r="A25" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B25" s="0">
-        <v>3</v>
+      <c r="B25" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>1</v>
+        <v>261</v>
       </c>
       <c r="D25" s="0" t="s">
         <v>237</v>
@@ -1204,11 +1705,11 @@
       <c r="A26" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B26" s="0">
-        <v>3</v>
+      <c r="B26" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>1</v>
+        <v>261</v>
       </c>
       <c r="D26" s="0" t="s">
         <v>237</v>
@@ -1221,11 +1722,11 @@
       <c r="A27" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B27" s="0">
-        <v>3</v>
+      <c r="B27" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>1</v>
+        <v>261</v>
       </c>
       <c r="D27" s="0" t="s">
         <v>237</v>
@@ -1238,11 +1739,11 @@
       <c r="A28" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B28" s="0">
-        <v>3</v>
+      <c r="B28" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>1</v>
+        <v>261</v>
       </c>
       <c r="D28" s="0" t="s">
         <v>237</v>
@@ -1255,11 +1756,11 @@
       <c r="A29" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B29" s="0">
-        <v>3</v>
+      <c r="B29" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>1</v>
+        <v>261</v>
       </c>
       <c r="D29" s="0" t="s">
         <v>237</v>
@@ -1272,11 +1773,11 @@
       <c r="A30" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B30" s="0">
-        <v>4</v>
+      <c r="B30" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>1</v>
+        <v>262</v>
       </c>
       <c r="D30" s="0" t="s">
         <v>237</v>
@@ -1289,11 +1790,11 @@
       <c r="A31" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B31" s="0">
-        <v>4</v>
+      <c r="B31" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>1</v>
+        <v>262</v>
       </c>
       <c r="D31" s="0" t="s">
         <v>237</v>
@@ -1306,11 +1807,11 @@
       <c r="A32" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B32" s="0">
-        <v>4</v>
+      <c r="B32" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>1</v>
+        <v>262</v>
       </c>
       <c r="D32" s="0" t="s">
         <v>237</v>
@@ -1323,11 +1824,11 @@
       <c r="A33" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B33" s="0">
-        <v>4</v>
+      <c r="B33" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>1</v>
+        <v>262</v>
       </c>
       <c r="D33" s="0" t="s">
         <v>237</v>
@@ -1340,11 +1841,11 @@
       <c r="A34" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B34" s="0">
-        <v>4</v>
+      <c r="B34" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>1</v>
+        <v>262</v>
       </c>
       <c r="D34" s="0" t="s">
         <v>237</v>
@@ -1357,11 +1858,11 @@
       <c r="A35" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B35" s="0">
-        <v>4</v>
+      <c r="B35" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>1</v>
+        <v>262</v>
       </c>
       <c r="D35" s="0" t="s">
         <v>237</v>
@@ -1374,11 +1875,11 @@
       <c r="A36" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B36" s="0">
-        <v>5</v>
+      <c r="B36" s="0" t="s">
+        <v>241</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>1</v>
+        <v>263</v>
       </c>
       <c r="D36" s="0" t="s">
         <v>237</v>
@@ -1391,11 +1892,11 @@
       <c r="A37" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B37" s="0">
-        <v>5</v>
+      <c r="B37" s="0" t="s">
+        <v>241</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>1</v>
+        <v>263</v>
       </c>
       <c r="D37" s="0" t="s">
         <v>237</v>
@@ -1408,11 +1909,11 @@
       <c r="A38" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B38" s="0">
-        <v>5</v>
+      <c r="B38" s="0" t="s">
+        <v>241</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>1</v>
+        <v>263</v>
       </c>
       <c r="D38" s="0" t="s">
         <v>237</v>
@@ -1425,11 +1926,11 @@
       <c r="A39" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B39" s="0">
-        <v>5</v>
+      <c r="B39" s="0" t="s">
+        <v>241</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>1</v>
+        <v>263</v>
       </c>
       <c r="D39" s="0" t="s">
         <v>237</v>
@@ -1442,11 +1943,11 @@
       <c r="A40" s="0" t="s">
         <v>181</v>
       </c>
-      <c r="B40" s="0">
-        <v>1</v>
+      <c r="B40" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>1</v>
+        <v>264</v>
       </c>
       <c r="D40" s="0" t="s">
         <v>237</v>
@@ -1459,11 +1960,11 @@
       <c r="A41" s="0" t="s">
         <v>181</v>
       </c>
-      <c r="B41" s="0">
-        <v>1</v>
+      <c r="B41" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>1</v>
+        <v>264</v>
       </c>
       <c r="D41" s="0" t="s">
         <v>237</v>
@@ -1476,11 +1977,11 @@
       <c r="A42" s="0" t="s">
         <v>181</v>
       </c>
-      <c r="B42" s="0">
-        <v>1</v>
+      <c r="B42" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>1</v>
+        <v>264</v>
       </c>
       <c r="D42" s="0" t="s">
         <v>237</v>
@@ -1493,11 +1994,11 @@
       <c r="A43" s="0" t="s">
         <v>181</v>
       </c>
-      <c r="B43" s="0">
-        <v>1</v>
+      <c r="B43" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>1</v>
+        <v>264</v>
       </c>
       <c r="D43" s="0" t="s">
         <v>237</v>
@@ -1510,11 +2011,11 @@
       <c r="A44" s="0" t="s">
         <v>181</v>
       </c>
-      <c r="B44" s="0">
-        <v>2</v>
+      <c r="B44" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>1</v>
+        <v>265</v>
       </c>
       <c r="D44" s="0" t="s">
         <v>237</v>
@@ -1527,11 +2028,11 @@
       <c r="A45" s="0" t="s">
         <v>181</v>
       </c>
-      <c r="B45" s="0">
-        <v>2</v>
+      <c r="B45" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>1</v>
+        <v>265</v>
       </c>
       <c r="D45" s="0" t="s">
         <v>237</v>
@@ -1544,11 +2045,11 @@
       <c r="A46" s="0" t="s">
         <v>181</v>
       </c>
-      <c r="B46" s="0">
-        <v>2</v>
+      <c r="B46" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>1</v>
+        <v>265</v>
       </c>
       <c r="D46" s="0" t="s">
         <v>237</v>
@@ -1561,11 +2062,11 @@
       <c r="A47" s="0" t="s">
         <v>181</v>
       </c>
-      <c r="B47" s="0">
-        <v>2</v>
+      <c r="B47" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>1</v>
+        <v>265</v>
       </c>
       <c r="D47" s="0" t="s">
         <v>237</v>
@@ -1578,11 +2079,11 @@
       <c r="A48" s="0" t="s">
         <v>181</v>
       </c>
-      <c r="B48" s="0">
-        <v>2</v>
+      <c r="B48" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>1</v>
+        <v>265</v>
       </c>
       <c r="D48" s="0" t="s">
         <v>237</v>
@@ -1595,11 +2096,11 @@
       <c r="A49" s="0" t="s">
         <v>181</v>
       </c>
-      <c r="B49" s="0">
-        <v>3</v>
+      <c r="B49" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>1</v>
+        <v>266</v>
       </c>
       <c r="D49" s="0" t="s">
         <v>237</v>
@@ -1612,11 +2113,11 @@
       <c r="A50" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="B50" s="0">
-        <v>1</v>
+      <c r="B50" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>1</v>
+        <v>267</v>
       </c>
       <c r="D50" s="0" t="s">
         <v>237</v>
@@ -1629,11 +2130,11 @@
       <c r="A51" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="B51" s="0">
-        <v>4</v>
+      <c r="B51" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>1</v>
+        <v>268</v>
       </c>
       <c r="D51" s="0" t="s">
         <v>237</v>
@@ -1646,11 +2147,11 @@
       <c r="A52" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="B52" s="0">
-        <v>4</v>
+      <c r="B52" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>1</v>
+        <v>268</v>
       </c>
       <c r="D52" s="0" t="s">
         <v>237</v>
@@ -1663,11 +2164,11 @@
       <c r="A53" s="0" t="s">
         <v>183</v>
       </c>
-      <c r="B53" s="0">
-        <v>2</v>
+      <c r="B53" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>1</v>
+        <v>269</v>
       </c>
       <c r="D53" s="0" t="s">
         <v>237</v>
@@ -1680,11 +2181,11 @@
       <c r="A54" s="0" t="s">
         <v>183</v>
       </c>
-      <c r="B54" s="0">
-        <v>4</v>
+      <c r="B54" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>1</v>
+        <v>270</v>
       </c>
       <c r="D54" s="0" t="s">
         <v>237</v>
@@ -1697,11 +2198,11 @@
       <c r="A55" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="B55" s="0">
-        <v>2</v>
+      <c r="B55" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>1</v>
+        <v>271</v>
       </c>
       <c r="D55" s="0" t="s">
         <v>237</v>
@@ -1714,11 +2215,11 @@
       <c r="A56" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="B56" s="0">
-        <v>3</v>
+      <c r="B56" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>1</v>
+        <v>272</v>
       </c>
       <c r="D56" s="0" t="s">
         <v>237</v>
@@ -1731,11 +2232,11 @@
       <c r="A57" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="B57" s="0">
-        <v>3</v>
+      <c r="B57" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>1</v>
+        <v>272</v>
       </c>
       <c r="D57" s="0" t="s">
         <v>237</v>
@@ -1748,11 +2249,11 @@
       <c r="A58" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="B58" s="0">
-        <v>3</v>
+      <c r="B58" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>1</v>
+        <v>272</v>
       </c>
       <c r="D58" s="0" t="s">
         <v>237</v>
@@ -1765,11 +2266,11 @@
       <c r="A59" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="B59" s="0">
-        <v>3</v>
+      <c r="B59" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>1</v>
+        <v>272</v>
       </c>
       <c r="D59" s="0" t="s">
         <v>237</v>
@@ -1782,11 +2283,11 @@
       <c r="A60" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="B60" s="0">
-        <v>3</v>
+      <c r="B60" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>1</v>
+        <v>272</v>
       </c>
       <c r="D60" s="0" t="s">
         <v>237</v>
@@ -1799,11 +2300,11 @@
       <c r="A61" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="B61" s="0">
-        <v>3</v>
+      <c r="B61" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>1</v>
+        <v>272</v>
       </c>
       <c r="D61" s="0" t="s">
         <v>237</v>
@@ -1816,11 +2317,11 @@
       <c r="A62" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="B62" s="0">
-        <v>3</v>
+      <c r="B62" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>1</v>
+        <v>272</v>
       </c>
       <c r="D62" s="0" t="s">
         <v>237</v>
@@ -1833,11 +2334,11 @@
       <c r="A63" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="B63" s="0">
-        <v>3</v>
+      <c r="B63" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>1</v>
+        <v>272</v>
       </c>
       <c r="D63" s="0" t="s">
         <v>237</v>
@@ -1850,11 +2351,11 @@
       <c r="A64" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="B64" s="0">
-        <v>4</v>
+      <c r="B64" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>1</v>
+        <v>273</v>
       </c>
       <c r="D64" s="0" t="s">
         <v>237</v>
@@ -1867,11 +2368,11 @@
       <c r="A65" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="B65" s="0">
-        <v>4</v>
+      <c r="B65" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>1</v>
+        <v>273</v>
       </c>
       <c r="D65" s="0" t="s">
         <v>237</v>
@@ -1884,11 +2385,11 @@
       <c r="A66" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="B66" s="0">
-        <v>4</v>
+      <c r="B66" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>1</v>
+        <v>273</v>
       </c>
       <c r="D66" s="0" t="s">
         <v>237</v>
@@ -1901,11 +2402,11 @@
       <c r="A67" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="B67" s="0">
-        <v>4</v>
+      <c r="B67" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>1</v>
+        <v>273</v>
       </c>
       <c r="D67" s="0" t="s">
         <v>237</v>
@@ -1918,11 +2419,11 @@
       <c r="A68" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="B68" s="0">
-        <v>4</v>
+      <c r="B68" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>1</v>
+        <v>273</v>
       </c>
       <c r="D68" s="0" t="s">
         <v>237</v>
@@ -1935,11 +2436,11 @@
       <c r="A69" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="B69" s="0">
-        <v>4</v>
+      <c r="B69" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>1</v>
+        <v>273</v>
       </c>
       <c r="D69" s="0" t="s">
         <v>237</v>
@@ -1952,11 +2453,11 @@
       <c r="A70" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="B70" s="0">
-        <v>4</v>
+      <c r="B70" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>1</v>
+        <v>273</v>
       </c>
       <c r="D70" s="0" t="s">
         <v>237</v>
@@ -1969,11 +2470,11 @@
       <c r="A71" s="0" t="s">
         <v>185</v>
       </c>
-      <c r="B71" s="0">
-        <v>3</v>
+      <c r="B71" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>1</v>
+        <v>274</v>
       </c>
       <c r="D71" s="0" t="s">
         <v>237</v>
@@ -1986,11 +2487,11 @@
       <c r="A72" s="0" t="s">
         <v>185</v>
       </c>
-      <c r="B72" s="0">
-        <v>3</v>
+      <c r="B72" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>1</v>
+        <v>274</v>
       </c>
       <c r="D72" s="0" t="s">
         <v>237</v>
@@ -2003,11 +2504,11 @@
       <c r="A73" s="0" t="s">
         <v>185</v>
       </c>
-      <c r="B73" s="0">
-        <v>3</v>
+      <c r="B73" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>1</v>
+        <v>274</v>
       </c>
       <c r="D73" s="0" t="s">
         <v>237</v>
@@ -2020,11 +2521,11 @@
       <c r="A74" s="0" t="s">
         <v>185</v>
       </c>
-      <c r="B74" s="0">
-        <v>4</v>
+      <c r="B74" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>1</v>
+        <v>275</v>
       </c>
       <c r="D74" s="0" t="s">
         <v>237</v>
@@ -2037,11 +2538,11 @@
       <c r="A75" s="0" t="s">
         <v>185</v>
       </c>
-      <c r="B75" s="0">
-        <v>4</v>
+      <c r="B75" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>1</v>
+        <v>275</v>
       </c>
       <c r="D75" s="0" t="s">
         <v>237</v>
@@ -2054,11 +2555,11 @@
       <c r="A76" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="B76" s="0">
-        <v>2</v>
+      <c r="B76" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>1</v>
+        <v>276</v>
       </c>
       <c r="D76" s="0" t="s">
         <v>237</v>
@@ -2071,11 +2572,11 @@
       <c r="A77" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="B77" s="0">
-        <v>2</v>
+      <c r="B77" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>1</v>
+        <v>276</v>
       </c>
       <c r="D77" s="0" t="s">
         <v>237</v>
@@ -2088,11 +2589,11 @@
       <c r="A78" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="B78" s="0">
-        <v>3</v>
+      <c r="B78" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>1</v>
+        <v>277</v>
       </c>
       <c r="D78" s="0" t="s">
         <v>237</v>
@@ -2105,11 +2606,11 @@
       <c r="A79" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="B79" s="0">
-        <v>3</v>
+      <c r="B79" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>1</v>
+        <v>277</v>
       </c>
       <c r="D79" s="0" t="s">
         <v>237</v>
@@ -2122,11 +2623,11 @@
       <c r="A80" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="B80" s="0">
-        <v>4</v>
+      <c r="B80" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>1</v>
+        <v>278</v>
       </c>
       <c r="D80" s="0" t="s">
         <v>237</v>
@@ -2139,11 +2640,11 @@
       <c r="A81" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="B81" s="0">
-        <v>4</v>
+      <c r="B81" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>1</v>
+        <v>278</v>
       </c>
       <c r="D81" s="0" t="s">
         <v>237</v>
@@ -2156,11 +2657,11 @@
       <c r="A82" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="B82" s="0">
-        <v>4</v>
+      <c r="B82" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>1</v>
+        <v>278</v>
       </c>
       <c r="D82" s="0" t="s">
         <v>237</v>
@@ -2173,11 +2674,11 @@
       <c r="A83" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="B83" s="0">
-        <v>1</v>
+      <c r="B83" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>1</v>
+        <v>279</v>
       </c>
       <c r="D83" s="0" t="s">
         <v>237</v>
@@ -2190,11 +2691,11 @@
       <c r="A84" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="B84" s="0">
-        <v>1</v>
+      <c r="B84" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>1</v>
+        <v>279</v>
       </c>
       <c r="D84" s="0" t="s">
         <v>237</v>
@@ -2207,11 +2708,11 @@
       <c r="A85" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="B85" s="0">
-        <v>1</v>
+      <c r="B85" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>1</v>
+        <v>279</v>
       </c>
       <c r="D85" s="0" t="s">
         <v>237</v>
@@ -2224,11 +2725,11 @@
       <c r="A86" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="B86" s="0">
-        <v>1</v>
+      <c r="B86" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>1</v>
+        <v>279</v>
       </c>
       <c r="D86" s="0" t="s">
         <v>237</v>
@@ -2241,11 +2742,11 @@
       <c r="A87" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="B87" s="0">
-        <v>1</v>
+      <c r="B87" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>1</v>
+        <v>279</v>
       </c>
       <c r="D87" s="0" t="s">
         <v>237</v>
@@ -2258,11 +2759,11 @@
       <c r="A88" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="B88" s="0">
-        <v>1</v>
+      <c r="B88" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C88" s="0" t="s">
-        <v>1</v>
+        <v>279</v>
       </c>
       <c r="D88" s="0" t="s">
         <v>237</v>
@@ -2275,11 +2776,11 @@
       <c r="A89" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="B89" s="0">
-        <v>1</v>
+      <c r="B89" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C89" s="0" t="s">
-        <v>1</v>
+        <v>279</v>
       </c>
       <c r="D89" s="0" t="s">
         <v>237</v>
@@ -2292,11 +2793,11 @@
       <c r="A90" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="B90" s="0">
-        <v>1</v>
+      <c r="B90" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>1</v>
+        <v>279</v>
       </c>
       <c r="D90" s="0" t="s">
         <v>237</v>
@@ -2309,11 +2810,11 @@
       <c r="A91" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="B91" s="0">
-        <v>2</v>
+      <c r="B91" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C91" s="0" t="s">
-        <v>1</v>
+        <v>280</v>
       </c>
       <c r="D91" s="0" t="s">
         <v>237</v>
@@ -2326,11 +2827,11 @@
       <c r="A92" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="B92" s="0">
-        <v>2</v>
+      <c r="B92" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C92" s="0" t="s">
-        <v>1</v>
+        <v>280</v>
       </c>
       <c r="D92" s="0" t="s">
         <v>237</v>
@@ -2343,11 +2844,11 @@
       <c r="A93" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="B93" s="0">
-        <v>2</v>
+      <c r="B93" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C93" s="0" t="s">
-        <v>1</v>
+        <v>280</v>
       </c>
       <c r="D93" s="0" t="s">
         <v>237</v>
@@ -2360,11 +2861,11 @@
       <c r="A94" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="B94" s="0">
-        <v>2</v>
+      <c r="B94" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C94" s="0" t="s">
-        <v>1</v>
+        <v>280</v>
       </c>
       <c r="D94" s="0" t="s">
         <v>237</v>
@@ -2377,11 +2878,11 @@
       <c r="A95" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="B95" s="0">
-        <v>2</v>
+      <c r="B95" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C95" s="0" t="s">
-        <v>1</v>
+        <v>280</v>
       </c>
       <c r="D95" s="0" t="s">
         <v>237</v>
@@ -2394,11 +2895,11 @@
       <c r="A96" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="B96" s="0">
-        <v>2</v>
+      <c r="B96" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C96" s="0" t="s">
-        <v>1</v>
+        <v>280</v>
       </c>
       <c r="D96" s="0" t="s">
         <v>237</v>
@@ -2411,11 +2912,11 @@
       <c r="A97" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="B97" s="0">
-        <v>3</v>
+      <c r="B97" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C97" s="0" t="s">
-        <v>1</v>
+        <v>281</v>
       </c>
       <c r="D97" s="0" t="s">
         <v>237</v>
@@ -2428,11 +2929,11 @@
       <c r="A98" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="B98" s="0">
-        <v>3</v>
+      <c r="B98" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C98" s="0" t="s">
-        <v>1</v>
+        <v>281</v>
       </c>
       <c r="D98" s="0" t="s">
         <v>237</v>
@@ -2445,11 +2946,11 @@
       <c r="A99" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="B99" s="0">
-        <v>3</v>
+      <c r="B99" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C99" s="0" t="s">
-        <v>1</v>
+        <v>281</v>
       </c>
       <c r="D99" s="0" t="s">
         <v>237</v>
@@ -2462,11 +2963,11 @@
       <c r="A100" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="B100" s="0">
-        <v>3</v>
+      <c r="B100" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C100" s="0" t="s">
-        <v>1</v>
+        <v>281</v>
       </c>
       <c r="D100" s="0" t="s">
         <v>237</v>
@@ -2479,11 +2980,11 @@
       <c r="A101" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="B101" s="0">
-        <v>3</v>
+      <c r="B101" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C101" s="0" t="s">
-        <v>1</v>
+        <v>281</v>
       </c>
       <c r="D101" s="0" t="s">
         <v>237</v>
@@ -2496,11 +2997,11 @@
       <c r="A102" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="B102" s="0">
-        <v>3</v>
+      <c r="B102" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C102" s="0" t="s">
-        <v>1</v>
+        <v>281</v>
       </c>
       <c r="D102" s="0" t="s">
         <v>237</v>
@@ -2513,11 +3014,11 @@
       <c r="A103" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="B103" s="0">
-        <v>4</v>
+      <c r="B103" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C103" s="0" t="s">
-        <v>1</v>
+        <v>282</v>
       </c>
       <c r="D103" s="0" t="s">
         <v>237</v>
@@ -2530,11 +3031,11 @@
       <c r="A104" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="B104" s="0">
-        <v>4</v>
+      <c r="B104" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C104" s="0" t="s">
-        <v>1</v>
+        <v>282</v>
       </c>
       <c r="D104" s="0" t="s">
         <v>237</v>
@@ -2547,11 +3048,11 @@
       <c r="A105" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="B105" s="0">
-        <v>4</v>
+      <c r="B105" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C105" s="0" t="s">
-        <v>1</v>
+        <v>282</v>
       </c>
       <c r="D105" s="0" t="s">
         <v>237</v>
@@ -2564,11 +3065,11 @@
       <c r="A106" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="B106" s="0">
-        <v>4</v>
+      <c r="B106" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C106" s="0" t="s">
-        <v>1</v>
+        <v>282</v>
       </c>
       <c r="D106" s="0" t="s">
         <v>237</v>
@@ -2581,11 +3082,11 @@
       <c r="A107" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="B107" s="0">
-        <v>4</v>
+      <c r="B107" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C107" s="0" t="s">
-        <v>1</v>
+        <v>282</v>
       </c>
       <c r="D107" s="0" t="s">
         <v>237</v>
@@ -2598,11 +3099,11 @@
       <c r="A108" s="0" t="s">
         <v>188</v>
       </c>
-      <c r="B108" s="0">
-        <v>2</v>
+      <c r="B108" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C108" s="0" t="s">
-        <v>1</v>
+        <v>283</v>
       </c>
       <c r="D108" s="0" t="s">
         <v>237</v>
@@ -2615,11 +3116,11 @@
       <c r="A109" s="0" t="s">
         <v>188</v>
       </c>
-      <c r="B109" s="0">
-        <v>2</v>
+      <c r="B109" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C109" s="0" t="s">
-        <v>1</v>
+        <v>283</v>
       </c>
       <c r="D109" s="0" t="s">
         <v>237</v>
@@ -2632,11 +3133,11 @@
       <c r="A110" s="0" t="s">
         <v>188</v>
       </c>
-      <c r="B110" s="0">
-        <v>2</v>
+      <c r="B110" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C110" s="0" t="s">
-        <v>1</v>
+        <v>283</v>
       </c>
       <c r="D110" s="0" t="s">
         <v>237</v>
@@ -2649,11 +3150,11 @@
       <c r="A111" s="0" t="s">
         <v>188</v>
       </c>
-      <c r="B111" s="0">
-        <v>2</v>
+      <c r="B111" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C111" s="0" t="s">
-        <v>1</v>
+        <v>283</v>
       </c>
       <c r="D111" s="0" t="s">
         <v>237</v>
@@ -2666,11 +3167,11 @@
       <c r="A112" s="0" t="s">
         <v>188</v>
       </c>
-      <c r="B112" s="0">
-        <v>2</v>
+      <c r="B112" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C112" s="0" t="s">
-        <v>1</v>
+        <v>283</v>
       </c>
       <c r="D112" s="0" t="s">
         <v>237</v>
@@ -2683,11 +3184,11 @@
       <c r="A113" s="0" t="s">
         <v>188</v>
       </c>
-      <c r="B113" s="0">
-        <v>2</v>
+      <c r="B113" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C113" s="0" t="s">
-        <v>1</v>
+        <v>283</v>
       </c>
       <c r="D113" s="0" t="s">
         <v>237</v>
@@ -2700,11 +3201,11 @@
       <c r="A114" s="0" t="s">
         <v>188</v>
       </c>
-      <c r="B114" s="0">
-        <v>3</v>
+      <c r="B114" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C114" s="0" t="s">
-        <v>1</v>
+        <v>284</v>
       </c>
       <c r="D114" s="0" t="s">
         <v>237</v>
@@ -2717,11 +3218,11 @@
       <c r="A115" s="0" t="s">
         <v>188</v>
       </c>
-      <c r="B115" s="0">
-        <v>3</v>
+      <c r="B115" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C115" s="0" t="s">
-        <v>1</v>
+        <v>284</v>
       </c>
       <c r="D115" s="0" t="s">
         <v>237</v>
@@ -2734,11 +3235,11 @@
       <c r="A116" s="0" t="s">
         <v>188</v>
       </c>
-      <c r="B116" s="0">
-        <v>3</v>
+      <c r="B116" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C116" s="0" t="s">
-        <v>1</v>
+        <v>284</v>
       </c>
       <c r="D116" s="0" t="s">
         <v>237</v>
@@ -2751,11 +3252,11 @@
       <c r="A117" s="0" t="s">
         <v>188</v>
       </c>
-      <c r="B117" s="0">
-        <v>3</v>
+      <c r="B117" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C117" s="0" t="s">
-        <v>1</v>
+        <v>284</v>
       </c>
       <c r="D117" s="0" t="s">
         <v>237</v>
@@ -2768,11 +3269,11 @@
       <c r="A118" s="0" t="s">
         <v>188</v>
       </c>
-      <c r="B118" s="0">
-        <v>4</v>
+      <c r="B118" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C118" s="0" t="s">
-        <v>1</v>
+        <v>285</v>
       </c>
       <c r="D118" s="0" t="s">
         <v>237</v>
@@ -2785,11 +3286,11 @@
       <c r="A119" s="0" t="s">
         <v>188</v>
       </c>
-      <c r="B119" s="0">
-        <v>4</v>
+      <c r="B119" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C119" s="0" t="s">
-        <v>1</v>
+        <v>285</v>
       </c>
       <c r="D119" s="0" t="s">
         <v>237</v>
@@ -2802,11 +3303,11 @@
       <c r="A120" s="0" t="s">
         <v>189</v>
       </c>
-      <c r="B120" s="0">
-        <v>1</v>
+      <c r="B120" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C120" s="0" t="s">
-        <v>1</v>
+        <v>286</v>
       </c>
       <c r="D120" s="0" t="s">
         <v>237</v>
@@ -2819,11 +3320,11 @@
       <c r="A121" s="0" t="s">
         <v>189</v>
       </c>
-      <c r="B121" s="0">
-        <v>1</v>
+      <c r="B121" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C121" s="0" t="s">
-        <v>1</v>
+        <v>286</v>
       </c>
       <c r="D121" s="0" t="s">
         <v>237</v>
@@ -2836,11 +3337,11 @@
       <c r="A122" s="0" t="s">
         <v>189</v>
       </c>
-      <c r="B122" s="0">
-        <v>1</v>
+      <c r="B122" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C122" s="0" t="s">
-        <v>1</v>
+        <v>286</v>
       </c>
       <c r="D122" s="0" t="s">
         <v>237</v>
@@ -2853,11 +3354,11 @@
       <c r="A123" s="0" t="s">
         <v>189</v>
       </c>
-      <c r="B123" s="0">
-        <v>1</v>
+      <c r="B123" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C123" s="0" t="s">
-        <v>1</v>
+        <v>286</v>
       </c>
       <c r="D123" s="0" t="s">
         <v>237</v>
@@ -2870,11 +3371,11 @@
       <c r="A124" s="0" t="s">
         <v>189</v>
       </c>
-      <c r="B124" s="0">
-        <v>2</v>
+      <c r="B124" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C124" s="0" t="s">
-        <v>1</v>
+        <v>287</v>
       </c>
       <c r="D124" s="0" t="s">
         <v>237</v>
@@ -2887,11 +3388,11 @@
       <c r="A125" s="0" t="s">
         <v>189</v>
       </c>
-      <c r="B125" s="0">
-        <v>2</v>
+      <c r="B125" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C125" s="0" t="s">
-        <v>1</v>
+        <v>287</v>
       </c>
       <c r="D125" s="0" t="s">
         <v>237</v>
@@ -2904,11 +3405,11 @@
       <c r="A126" s="0" t="s">
         <v>189</v>
       </c>
-      <c r="B126" s="0">
-        <v>3</v>
+      <c r="B126" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C126" s="0" t="s">
-        <v>1</v>
+        <v>288</v>
       </c>
       <c r="D126" s="0" t="s">
         <v>237</v>
@@ -2921,11 +3422,11 @@
       <c r="A127" s="0" t="s">
         <v>189</v>
       </c>
-      <c r="B127" s="0">
-        <v>3</v>
+      <c r="B127" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C127" s="0" t="s">
-        <v>1</v>
+        <v>288</v>
       </c>
       <c r="D127" s="0" t="s">
         <v>237</v>
@@ -2938,11 +3439,11 @@
       <c r="A128" s="0" t="s">
         <v>189</v>
       </c>
-      <c r="B128" s="0">
-        <v>3</v>
+      <c r="B128" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C128" s="0" t="s">
-        <v>1</v>
+        <v>288</v>
       </c>
       <c r="D128" s="0" t="s">
         <v>237</v>
@@ -2955,11 +3456,11 @@
       <c r="A129" s="0" t="s">
         <v>189</v>
       </c>
-      <c r="B129" s="0">
-        <v>3</v>
+      <c r="B129" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C129" s="0" t="s">
-        <v>1</v>
+        <v>288</v>
       </c>
       <c r="D129" s="0" t="s">
         <v>237</v>
@@ -2972,11 +3473,11 @@
       <c r="A130" s="0" t="s">
         <v>189</v>
       </c>
-      <c r="B130" s="0">
-        <v>4</v>
+      <c r="B130" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C130" s="0" t="s">
-        <v>1</v>
+        <v>289</v>
       </c>
       <c r="D130" s="0" t="s">
         <v>237</v>
@@ -2989,11 +3490,11 @@
       <c r="A131" s="0" t="s">
         <v>189</v>
       </c>
-      <c r="B131" s="0">
-        <v>4</v>
+      <c r="B131" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C131" s="0" t="s">
-        <v>1</v>
+        <v>289</v>
       </c>
       <c r="D131" s="0" t="s">
         <v>237</v>
@@ -3006,11 +3507,11 @@
       <c r="A132" s="0" t="s">
         <v>189</v>
       </c>
-      <c r="B132" s="0">
-        <v>4</v>
+      <c r="B132" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C132" s="0" t="s">
-        <v>1</v>
+        <v>289</v>
       </c>
       <c r="D132" s="0" t="s">
         <v>237</v>
@@ -3023,11 +3524,11 @@
       <c r="A133" s="0" t="s">
         <v>189</v>
       </c>
-      <c r="B133" s="0">
-        <v>4</v>
+      <c r="B133" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C133" s="0" t="s">
-        <v>1</v>
+        <v>289</v>
       </c>
       <c r="D133" s="0" t="s">
         <v>237</v>
@@ -3040,11 +3541,11 @@
       <c r="A134" s="0" t="s">
         <v>189</v>
       </c>
-      <c r="B134" s="0">
-        <v>4</v>
+      <c r="B134" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C134" s="0" t="s">
-        <v>1</v>
+        <v>289</v>
       </c>
       <c r="D134" s="0" t="s">
         <v>237</v>
@@ -3057,11 +3558,11 @@
       <c r="A135" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B135" s="0">
-        <v>1</v>
+      <c r="B135" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C135" s="0" t="s">
-        <v>1</v>
+        <v>290</v>
       </c>
       <c r="D135" s="0" t="s">
         <v>237</v>
@@ -3074,11 +3575,11 @@
       <c r="A136" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B136" s="0">
-        <v>1</v>
+      <c r="B136" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C136" s="0" t="s">
-        <v>1</v>
+        <v>290</v>
       </c>
       <c r="D136" s="0" t="s">
         <v>237</v>
@@ -3091,11 +3592,11 @@
       <c r="A137" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B137" s="0">
-        <v>1</v>
+      <c r="B137" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C137" s="0" t="s">
-        <v>1</v>
+        <v>290</v>
       </c>
       <c r="D137" s="0" t="s">
         <v>237</v>
@@ -3108,11 +3609,11 @@
       <c r="A138" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B138" s="0">
-        <v>1</v>
+      <c r="B138" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C138" s="0" t="s">
-        <v>1</v>
+        <v>290</v>
       </c>
       <c r="D138" s="0" t="s">
         <v>237</v>
@@ -3125,11 +3626,11 @@
       <c r="A139" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B139" s="0">
-        <v>1</v>
+      <c r="B139" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C139" s="0" t="s">
-        <v>1</v>
+        <v>290</v>
       </c>
       <c r="D139" s="0" t="s">
         <v>237</v>
@@ -3142,11 +3643,11 @@
       <c r="A140" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B140" s="0">
-        <v>2</v>
+      <c r="B140" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C140" s="0" t="s">
-        <v>1</v>
+        <v>291</v>
       </c>
       <c r="D140" s="0" t="s">
         <v>237</v>
@@ -3159,11 +3660,11 @@
       <c r="A141" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B141" s="0">
-        <v>2</v>
+      <c r="B141" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C141" s="0" t="s">
-        <v>1</v>
+        <v>291</v>
       </c>
       <c r="D141" s="0" t="s">
         <v>237</v>
@@ -3176,11 +3677,11 @@
       <c r="A142" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B142" s="0">
-        <v>2</v>
+      <c r="B142" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C142" s="0" t="s">
-        <v>1</v>
+        <v>291</v>
       </c>
       <c r="D142" s="0" t="s">
         <v>237</v>
@@ -3193,11 +3694,11 @@
       <c r="A143" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B143" s="0">
-        <v>2</v>
+      <c r="B143" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C143" s="0" t="s">
-        <v>1</v>
+        <v>291</v>
       </c>
       <c r="D143" s="0" t="s">
         <v>237</v>
@@ -3210,11 +3711,11 @@
       <c r="A144" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B144" s="0">
-        <v>2</v>
+      <c r="B144" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C144" s="0" t="s">
-        <v>1</v>
+        <v>291</v>
       </c>
       <c r="D144" s="0" t="s">
         <v>237</v>
@@ -3227,11 +3728,11 @@
       <c r="A145" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B145" s="0">
-        <v>2</v>
+      <c r="B145" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C145" s="0" t="s">
-        <v>1</v>
+        <v>291</v>
       </c>
       <c r="D145" s="0" t="s">
         <v>237</v>
@@ -3244,11 +3745,11 @@
       <c r="A146" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B146" s="0">
-        <v>3</v>
+      <c r="B146" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C146" s="0" t="s">
-        <v>1</v>
+        <v>292</v>
       </c>
       <c r="D146" s="0" t="s">
         <v>237</v>
@@ -3261,11 +3762,11 @@
       <c r="A147" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B147" s="0">
-        <v>3</v>
+      <c r="B147" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C147" s="0" t="s">
-        <v>1</v>
+        <v>292</v>
       </c>
       <c r="D147" s="0" t="s">
         <v>237</v>
@@ -3278,11 +3779,11 @@
       <c r="A148" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B148" s="0">
-        <v>3</v>
+      <c r="B148" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C148" s="0" t="s">
-        <v>1</v>
+        <v>292</v>
       </c>
       <c r="D148" s="0" t="s">
         <v>237</v>
@@ -3295,11 +3796,11 @@
       <c r="A149" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B149" s="0">
-        <v>3</v>
+      <c r="B149" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C149" s="0" t="s">
-        <v>1</v>
+        <v>292</v>
       </c>
       <c r="D149" s="0" t="s">
         <v>237</v>
@@ -3312,11 +3813,11 @@
       <c r="A150" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B150" s="0">
-        <v>3</v>
+      <c r="B150" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C150" s="0" t="s">
-        <v>1</v>
+        <v>292</v>
       </c>
       <c r="D150" s="0" t="s">
         <v>237</v>
@@ -3329,11 +3830,11 @@
       <c r="A151" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B151" s="0">
-        <v>3</v>
+      <c r="B151" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C151" s="0" t="s">
-        <v>1</v>
+        <v>292</v>
       </c>
       <c r="D151" s="0" t="s">
         <v>237</v>
@@ -3346,11 +3847,11 @@
       <c r="A152" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B152" s="0">
-        <v>3</v>
+      <c r="B152" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C152" s="0" t="s">
-        <v>1</v>
+        <v>292</v>
       </c>
       <c r="D152" s="0" t="s">
         <v>237</v>
@@ -3363,11 +3864,11 @@
       <c r="A153" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B153" s="0">
-        <v>4</v>
+      <c r="B153" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C153" s="0" t="s">
-        <v>1</v>
+        <v>293</v>
       </c>
       <c r="D153" s="0" t="s">
         <v>237</v>
@@ -3380,11 +3881,11 @@
       <c r="A154" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B154" s="0">
-        <v>4</v>
+      <c r="B154" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C154" s="0" t="s">
-        <v>1</v>
+        <v>293</v>
       </c>
       <c r="D154" s="0" t="s">
         <v>237</v>
@@ -3397,11 +3898,11 @@
       <c r="A155" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B155" s="0">
-        <v>4</v>
+      <c r="B155" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C155" s="0" t="s">
-        <v>1</v>
+        <v>293</v>
       </c>
       <c r="D155" s="0" t="s">
         <v>237</v>
@@ -3414,11 +3915,11 @@
       <c r="A156" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B156" s="0">
-        <v>4</v>
+      <c r="B156" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C156" s="0" t="s">
-        <v>1</v>
+        <v>293</v>
       </c>
       <c r="D156" s="0" t="s">
         <v>237</v>
@@ -3431,11 +3932,11 @@
       <c r="A157" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B157" s="0">
-        <v>4</v>
+      <c r="B157" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C157" s="0" t="s">
-        <v>1</v>
+        <v>293</v>
       </c>
       <c r="D157" s="0" t="s">
         <v>237</v>
@@ -3448,11 +3949,11 @@
       <c r="A158" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B158" s="0">
-        <v>4</v>
+      <c r="B158" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C158" s="0" t="s">
-        <v>1</v>
+        <v>293</v>
       </c>
       <c r="D158" s="0" t="s">
         <v>237</v>
@@ -3465,11 +3966,11 @@
       <c r="A159" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B159" s="0">
-        <v>4</v>
+      <c r="B159" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C159" s="0" t="s">
-        <v>1</v>
+        <v>293</v>
       </c>
       <c r="D159" s="0" t="s">
         <v>237</v>
@@ -3482,11 +3983,11 @@
       <c r="A160" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B160" s="0">
-        <v>4</v>
+      <c r="B160" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C160" s="0" t="s">
-        <v>1</v>
+        <v>293</v>
       </c>
       <c r="D160" s="0" t="s">
         <v>237</v>
@@ -3499,11 +4000,11 @@
       <c r="A161" s="0" t="s">
         <v>191</v>
       </c>
-      <c r="B161" s="0">
-        <v>3</v>
+      <c r="B161" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C161" s="0" t="s">
-        <v>1</v>
+        <v>294</v>
       </c>
       <c r="D161" s="0" t="s">
         <v>237</v>
@@ -3516,11 +4017,11 @@
       <c r="A162" s="0" t="s">
         <v>191</v>
       </c>
-      <c r="B162" s="0">
-        <v>3</v>
+      <c r="B162" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C162" s="0" t="s">
-        <v>1</v>
+        <v>294</v>
       </c>
       <c r="D162" s="0" t="s">
         <v>237</v>
@@ -3533,11 +4034,11 @@
       <c r="A163" s="0" t="s">
         <v>191</v>
       </c>
-      <c r="B163" s="0">
-        <v>3</v>
+      <c r="B163" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C163" s="0" t="s">
-        <v>1</v>
+        <v>294</v>
       </c>
       <c r="D163" s="0" t="s">
         <v>237</v>
@@ -3550,11 +4051,11 @@
       <c r="A164" s="0" t="s">
         <v>191</v>
       </c>
-      <c r="B164" s="0">
-        <v>3</v>
+      <c r="B164" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C164" s="0" t="s">
-        <v>1</v>
+        <v>294</v>
       </c>
       <c r="D164" s="0" t="s">
         <v>237</v>
@@ -3567,11 +4068,11 @@
       <c r="A165" s="0" t="s">
         <v>191</v>
       </c>
-      <c r="B165" s="0">
-        <v>3</v>
+      <c r="B165" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C165" s="0" t="s">
-        <v>1</v>
+        <v>294</v>
       </c>
       <c r="D165" s="0" t="s">
         <v>237</v>
@@ -3584,11 +4085,11 @@
       <c r="A166" s="0" t="s">
         <v>191</v>
       </c>
-      <c r="B166" s="0">
-        <v>3</v>
+      <c r="B166" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C166" s="0" t="s">
-        <v>1</v>
+        <v>294</v>
       </c>
       <c r="D166" s="0" t="s">
         <v>237</v>
@@ -3601,11 +4102,11 @@
       <c r="A167" s="0" t="s">
         <v>191</v>
       </c>
-      <c r="B167" s="0">
-        <v>4</v>
+      <c r="B167" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C167" s="0" t="s">
-        <v>1</v>
+        <v>295</v>
       </c>
       <c r="D167" s="0" t="s">
         <v>237</v>
@@ -3618,11 +4119,11 @@
       <c r="A168" s="0" t="s">
         <v>191</v>
       </c>
-      <c r="B168" s="0">
-        <v>4</v>
+      <c r="B168" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C168" s="0" t="s">
-        <v>1</v>
+        <v>295</v>
       </c>
       <c r="D168" s="0" t="s">
         <v>237</v>
@@ -3635,11 +4136,11 @@
       <c r="A169" s="0" t="s">
         <v>191</v>
       </c>
-      <c r="B169" s="0">
-        <v>4</v>
+      <c r="B169" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C169" s="0" t="s">
-        <v>1</v>
+        <v>295</v>
       </c>
       <c r="D169" s="0" t="s">
         <v>237</v>
@@ -3652,11 +4153,11 @@
       <c r="A170" s="0" t="s">
         <v>191</v>
       </c>
-      <c r="B170" s="0">
-        <v>4</v>
+      <c r="B170" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C170" s="0" t="s">
-        <v>1</v>
+        <v>295</v>
       </c>
       <c r="D170" s="0" t="s">
         <v>237</v>
@@ -3669,11 +4170,11 @@
       <c r="A171" s="0" t="s">
         <v>191</v>
       </c>
-      <c r="B171" s="0">
-        <v>4</v>
+      <c r="B171" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C171" s="0" t="s">
-        <v>1</v>
+        <v>295</v>
       </c>
       <c r="D171" s="0" t="s">
         <v>237</v>
@@ -3686,11 +4187,11 @@
       <c r="A172" s="0" t="s">
         <v>191</v>
       </c>
-      <c r="B172" s="0">
-        <v>4</v>
+      <c r="B172" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C172" s="0" t="s">
-        <v>1</v>
+        <v>295</v>
       </c>
       <c r="D172" s="0" t="s">
         <v>237</v>
@@ -3703,11 +4204,11 @@
       <c r="A173" s="0" t="s">
         <v>191</v>
       </c>
-      <c r="B173" s="0">
-        <v>4</v>
+      <c r="B173" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C173" s="0" t="s">
-        <v>1</v>
+        <v>295</v>
       </c>
       <c r="D173" s="0" t="s">
         <v>237</v>
@@ -3720,11 +4221,11 @@
       <c r="A174" s="0" t="s">
         <v>191</v>
       </c>
-      <c r="B174" s="0">
-        <v>4</v>
+      <c r="B174" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C174" s="0" t="s">
-        <v>1</v>
+        <v>295</v>
       </c>
       <c r="D174" s="0" t="s">
         <v>237</v>
@@ -3737,11 +4238,11 @@
       <c r="A175" s="0" t="s">
         <v>192</v>
       </c>
-      <c r="B175" s="0">
-        <v>1</v>
+      <c r="B175" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C175" s="0" t="s">
-        <v>1</v>
+        <v>296</v>
       </c>
       <c r="D175" s="0" t="s">
         <v>237</v>
@@ -3754,11 +4255,11 @@
       <c r="A176" s="0" t="s">
         <v>192</v>
       </c>
-      <c r="B176" s="0">
-        <v>2</v>
+      <c r="B176" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C176" s="0" t="s">
-        <v>1</v>
+        <v>297</v>
       </c>
       <c r="D176" s="0" t="s">
         <v>237</v>
@@ -3771,11 +4272,11 @@
       <c r="A177" s="0" t="s">
         <v>193</v>
       </c>
-      <c r="B177" s="0">
-        <v>1</v>
+      <c r="B177" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C177" s="0" t="s">
-        <v>1</v>
+        <v>298</v>
       </c>
       <c r="D177" s="0" t="s">
         <v>237</v>
@@ -3788,11 +4289,11 @@
       <c r="A178" s="0" t="s">
         <v>193</v>
       </c>
-      <c r="B178" s="0">
-        <v>1</v>
+      <c r="B178" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C178" s="0" t="s">
-        <v>1</v>
+        <v>298</v>
       </c>
       <c r="D178" s="0" t="s">
         <v>237</v>
@@ -3805,11 +4306,11 @@
       <c r="A179" s="0" t="s">
         <v>193</v>
       </c>
-      <c r="B179" s="0">
-        <v>1</v>
+      <c r="B179" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C179" s="0" t="s">
-        <v>1</v>
+        <v>298</v>
       </c>
       <c r="D179" s="0" t="s">
         <v>237</v>
@@ -3822,11 +4323,11 @@
       <c r="A180" s="0" t="s">
         <v>193</v>
       </c>
-      <c r="B180" s="0">
-        <v>2</v>
+      <c r="B180" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C180" s="0" t="s">
-        <v>1</v>
+        <v>299</v>
       </c>
       <c r="D180" s="0" t="s">
         <v>237</v>
@@ -3839,11 +4340,11 @@
       <c r="A181" s="0" t="s">
         <v>193</v>
       </c>
-      <c r="B181" s="0">
-        <v>2</v>
+      <c r="B181" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C181" s="0" t="s">
-        <v>1</v>
+        <v>299</v>
       </c>
       <c r="D181" s="0" t="s">
         <v>237</v>
@@ -3856,11 +4357,11 @@
       <c r="A182" s="0" t="s">
         <v>193</v>
       </c>
-      <c r="B182" s="0">
-        <v>2</v>
+      <c r="B182" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C182" s="0" t="s">
-        <v>1</v>
+        <v>299</v>
       </c>
       <c r="D182" s="0" t="s">
         <v>237</v>
@@ -3873,11 +4374,11 @@
       <c r="A183" s="0" t="s">
         <v>193</v>
       </c>
-      <c r="B183" s="0">
-        <v>2</v>
+      <c r="B183" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C183" s="0" t="s">
-        <v>1</v>
+        <v>299</v>
       </c>
       <c r="D183" s="0" t="s">
         <v>237</v>
@@ -3890,11 +4391,11 @@
       <c r="A184" s="0" t="s">
         <v>193</v>
       </c>
-      <c r="B184" s="0">
-        <v>2</v>
+      <c r="B184" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C184" s="0" t="s">
-        <v>1</v>
+        <v>299</v>
       </c>
       <c r="D184" s="0" t="s">
         <v>237</v>
@@ -3907,11 +4408,11 @@
       <c r="A185" s="0" t="s">
         <v>193</v>
       </c>
-      <c r="B185" s="0">
-        <v>3</v>
+      <c r="B185" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C185" s="0" t="s">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="D185" s="0" t="s">
         <v>237</v>
@@ -3924,11 +4425,11 @@
       <c r="A186" s="0" t="s">
         <v>193</v>
       </c>
-      <c r="B186" s="0">
-        <v>3</v>
+      <c r="B186" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C186" s="0" t="s">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="D186" s="0" t="s">
         <v>237</v>
@@ -3941,11 +4442,11 @@
       <c r="A187" s="0" t="s">
         <v>193</v>
       </c>
-      <c r="B187" s="0">
-        <v>3</v>
+      <c r="B187" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C187" s="0" t="s">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="D187" s="0" t="s">
         <v>237</v>
@@ -3958,11 +4459,11 @@
       <c r="A188" s="0" t="s">
         <v>193</v>
       </c>
-      <c r="B188" s="0">
-        <v>4</v>
+      <c r="B188" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C188" s="0" t="s">
-        <v>1</v>
+        <v>301</v>
       </c>
       <c r="D188" s="0" t="s">
         <v>237</v>
@@ -3975,11 +4476,11 @@
       <c r="A189" s="0" t="s">
         <v>193</v>
       </c>
-      <c r="B189" s="0">
-        <v>4</v>
+      <c r="B189" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C189" s="0" t="s">
-        <v>1</v>
+        <v>301</v>
       </c>
       <c r="D189" s="0" t="s">
         <v>237</v>
@@ -3992,11 +4493,11 @@
       <c r="A190" s="0" t="s">
         <v>193</v>
       </c>
-      <c r="B190" s="0">
-        <v>4</v>
+      <c r="B190" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C190" s="0" t="s">
-        <v>1</v>
+        <v>301</v>
       </c>
       <c r="D190" s="0" t="s">
         <v>237</v>
@@ -4009,11 +4510,11 @@
       <c r="A191" s="0" t="s">
         <v>193</v>
       </c>
-      <c r="B191" s="0">
-        <v>4</v>
+      <c r="B191" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C191" s="0" t="s">
-        <v>1</v>
+        <v>301</v>
       </c>
       <c r="D191" s="0" t="s">
         <v>237</v>
@@ -4026,11 +4527,11 @@
       <c r="A192" s="0" t="s">
         <v>193</v>
       </c>
-      <c r="B192" s="0">
-        <v>4</v>
+      <c r="B192" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C192" s="0" t="s">
-        <v>1</v>
+        <v>301</v>
       </c>
       <c r="D192" s="0" t="s">
         <v>237</v>
@@ -4043,11 +4544,11 @@
       <c r="A193" s="0" t="s">
         <v>194</v>
       </c>
-      <c r="B193" s="0">
-        <v>1</v>
+      <c r="B193" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C193" s="0" t="s">
-        <v>1</v>
+        <v>302</v>
       </c>
       <c r="D193" s="0" t="s">
         <v>237</v>
@@ -4060,11 +4561,11 @@
       <c r="A194" s="0" t="s">
         <v>194</v>
       </c>
-      <c r="B194" s="0">
-        <v>2</v>
+      <c r="B194" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C194" s="0" t="s">
-        <v>1</v>
+        <v>303</v>
       </c>
       <c r="D194" s="0" t="s">
         <v>237</v>
@@ -4077,11 +4578,11 @@
       <c r="A195" s="0" t="s">
         <v>194</v>
       </c>
-      <c r="B195" s="0">
-        <v>2</v>
+      <c r="B195" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C195" s="0" t="s">
-        <v>1</v>
+        <v>303</v>
       </c>
       <c r="D195" s="0" t="s">
         <v>237</v>
@@ -4094,11 +4595,11 @@
       <c r="A196" s="0" t="s">
         <v>194</v>
       </c>
-      <c r="B196" s="0">
-        <v>2</v>
+      <c r="B196" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C196" s="0" t="s">
-        <v>1</v>
+        <v>303</v>
       </c>
       <c r="D196" s="0" t="s">
         <v>237</v>
@@ -4111,11 +4612,11 @@
       <c r="A197" s="0" t="s">
         <v>194</v>
       </c>
-      <c r="B197" s="0">
-        <v>3</v>
+      <c r="B197" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C197" s="0" t="s">
-        <v>1</v>
+        <v>304</v>
       </c>
       <c r="D197" s="0" t="s">
         <v>237</v>
@@ -4128,11 +4629,11 @@
       <c r="A198" s="0" t="s">
         <v>194</v>
       </c>
-      <c r="B198" s="0">
-        <v>3</v>
+      <c r="B198" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C198" s="0" t="s">
-        <v>1</v>
+        <v>304</v>
       </c>
       <c r="D198" s="0" t="s">
         <v>237</v>
@@ -4145,11 +4646,11 @@
       <c r="A199" s="0" t="s">
         <v>194</v>
       </c>
-      <c r="B199" s="0">
-        <v>3</v>
+      <c r="B199" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C199" s="0" t="s">
-        <v>1</v>
+        <v>304</v>
       </c>
       <c r="D199" s="0" t="s">
         <v>237</v>
@@ -4162,11 +4663,11 @@
       <c r="A200" s="0" t="s">
         <v>194</v>
       </c>
-      <c r="B200" s="0">
-        <v>4</v>
+      <c r="B200" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C200" s="0" t="s">
-        <v>1</v>
+        <v>305</v>
       </c>
       <c r="D200" s="0" t="s">
         <v>237</v>
@@ -4179,11 +4680,11 @@
       <c r="A201" s="0" t="s">
         <v>194</v>
       </c>
-      <c r="B201" s="0">
-        <v>4</v>
+      <c r="B201" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C201" s="0" t="s">
-        <v>1</v>
+        <v>305</v>
       </c>
       <c r="D201" s="0" t="s">
         <v>237</v>
@@ -4196,11 +4697,11 @@
       <c r="A202" s="0" t="s">
         <v>194</v>
       </c>
-      <c r="B202" s="0">
-        <v>4</v>
+      <c r="B202" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C202" s="0" t="s">
-        <v>1</v>
+        <v>305</v>
       </c>
       <c r="D202" s="0" t="s">
         <v>237</v>
@@ -4213,11 +4714,11 @@
       <c r="A203" s="0" t="s">
         <v>194</v>
       </c>
-      <c r="B203" s="0">
-        <v>4</v>
+      <c r="B203" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C203" s="0" t="s">
-        <v>1</v>
+        <v>305</v>
       </c>
       <c r="D203" s="0" t="s">
         <v>237</v>
@@ -4230,11 +4731,11 @@
       <c r="A204" s="0" t="s">
         <v>194</v>
       </c>
-      <c r="B204" s="0">
-        <v>4</v>
+      <c r="B204" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C204" s="0" t="s">
-        <v>1</v>
+        <v>305</v>
       </c>
       <c r="D204" s="0" t="s">
         <v>237</v>
@@ -4247,11 +4748,11 @@
       <c r="A205" s="0" t="s">
         <v>194</v>
       </c>
-      <c r="B205" s="0">
-        <v>4</v>
+      <c r="B205" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C205" s="0" t="s">
-        <v>1</v>
+        <v>305</v>
       </c>
       <c r="D205" s="0" t="s">
         <v>237</v>
@@ -4264,11 +4765,11 @@
       <c r="A206" s="0" t="s">
         <v>194</v>
       </c>
-      <c r="B206" s="0">
-        <v>4</v>
+      <c r="B206" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C206" s="0" t="s">
-        <v>1</v>
+        <v>305</v>
       </c>
       <c r="D206" s="0" t="s">
         <v>237</v>
@@ -4281,11 +4782,11 @@
       <c r="A207" s="0" t="s">
         <v>195</v>
       </c>
-      <c r="B207" s="0">
-        <v>2</v>
+      <c r="B207" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C207" s="0" t="s">
-        <v>1</v>
+        <v>306</v>
       </c>
       <c r="D207" s="0" t="s">
         <v>237</v>
@@ -4298,11 +4799,11 @@
       <c r="A208" s="0" t="s">
         <v>195</v>
       </c>
-      <c r="B208" s="0">
-        <v>2</v>
+      <c r="B208" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C208" s="0" t="s">
-        <v>1</v>
+        <v>306</v>
       </c>
       <c r="D208" s="0" t="s">
         <v>237</v>
@@ -4315,11 +4816,11 @@
       <c r="A209" s="0" t="s">
         <v>195</v>
       </c>
-      <c r="B209" s="0">
-        <v>4</v>
+      <c r="B209" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C209" s="0" t="s">
-        <v>1</v>
+        <v>307</v>
       </c>
       <c r="D209" s="0" t="s">
         <v>237</v>
@@ -4332,11 +4833,11 @@
       <c r="A210" s="0" t="s">
         <v>195</v>
       </c>
-      <c r="B210" s="0">
-        <v>4</v>
+      <c r="B210" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C210" s="0" t="s">
-        <v>1</v>
+        <v>307</v>
       </c>
       <c r="D210" s="0" t="s">
         <v>237</v>
@@ -4349,11 +4850,11 @@
       <c r="A211" s="0" t="s">
         <v>196</v>
       </c>
-      <c r="B211" s="0">
-        <v>2</v>
+      <c r="B211" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C211" s="0" t="s">
-        <v>1</v>
+        <v>308</v>
       </c>
       <c r="D211" s="0" t="s">
         <v>237</v>
@@ -4366,11 +4867,11 @@
       <c r="A212" s="0" t="s">
         <v>196</v>
       </c>
-      <c r="B212" s="0">
-        <v>4</v>
+      <c r="B212" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C212" s="0" t="s">
-        <v>1</v>
+        <v>309</v>
       </c>
       <c r="D212" s="0" t="s">
         <v>237</v>
@@ -4383,11 +4884,11 @@
       <c r="A213" s="0" t="s">
         <v>196</v>
       </c>
-      <c r="B213" s="0">
-        <v>4</v>
+      <c r="B213" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C213" s="0" t="s">
-        <v>1</v>
+        <v>309</v>
       </c>
       <c r="D213" s="0" t="s">
         <v>237</v>
@@ -4400,11 +4901,11 @@
       <c r="A214" s="0" t="s">
         <v>196</v>
       </c>
-      <c r="B214" s="0">
-        <v>4</v>
+      <c r="B214" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C214" s="0" t="s">
-        <v>1</v>
+        <v>309</v>
       </c>
       <c r="D214" s="0" t="s">
         <v>237</v>
@@ -4417,11 +4918,11 @@
       <c r="A215" s="0" t="s">
         <v>197</v>
       </c>
-      <c r="B215" s="0">
-        <v>1</v>
+      <c r="B215" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C215" s="0" t="s">
-        <v>1</v>
+        <v>310</v>
       </c>
       <c r="D215" s="0" t="s">
         <v>237</v>
@@ -4434,11 +4935,11 @@
       <c r="A216" s="0" t="s">
         <v>197</v>
       </c>
-      <c r="B216" s="0">
-        <v>1</v>
+      <c r="B216" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C216" s="0" t="s">
-        <v>1</v>
+        <v>310</v>
       </c>
       <c r="D216" s="0" t="s">
         <v>237</v>
@@ -4451,11 +4952,11 @@
       <c r="A217" s="0" t="s">
         <v>197</v>
       </c>
-      <c r="B217" s="0">
-        <v>1</v>
+      <c r="B217" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C217" s="0" t="s">
-        <v>1</v>
+        <v>310</v>
       </c>
       <c r="D217" s="0" t="s">
         <v>237</v>
@@ -4468,11 +4969,11 @@
       <c r="A218" s="0" t="s">
         <v>197</v>
       </c>
-      <c r="B218" s="0">
-        <v>2</v>
+      <c r="B218" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C218" s="0" t="s">
-        <v>1</v>
+        <v>311</v>
       </c>
       <c r="D218" s="0" t="s">
         <v>237</v>
@@ -4485,11 +4986,11 @@
       <c r="A219" s="0" t="s">
         <v>197</v>
       </c>
-      <c r="B219" s="0">
-        <v>4</v>
+      <c r="B219" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C219" s="0" t="s">
-        <v>1</v>
+        <v>312</v>
       </c>
       <c r="D219" s="0" t="s">
         <v>237</v>
@@ -4502,11 +5003,11 @@
       <c r="A220" s="0" t="s">
         <v>197</v>
       </c>
-      <c r="B220" s="0">
-        <v>4</v>
+      <c r="B220" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C220" s="0" t="s">
-        <v>1</v>
+        <v>312</v>
       </c>
       <c r="D220" s="0" t="s">
         <v>237</v>
@@ -4519,11 +5020,11 @@
       <c r="A221" s="0" t="s">
         <v>198</v>
       </c>
-      <c r="B221" s="0">
-        <v>4</v>
+      <c r="B221" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C221" s="0" t="s">
-        <v>1</v>
+        <v>313</v>
       </c>
       <c r="D221" s="0" t="s">
         <v>237</v>
@@ -4536,11 +5037,11 @@
       <c r="A222" s="0" t="s">
         <v>198</v>
       </c>
-      <c r="B222" s="0">
-        <v>4</v>
+      <c r="B222" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C222" s="0" t="s">
-        <v>1</v>
+        <v>313</v>
       </c>
       <c r="D222" s="0" t="s">
         <v>237</v>
@@ -4553,11 +5054,11 @@
       <c r="A223" s="0" t="s">
         <v>199</v>
       </c>
-      <c r="B223" s="0">
-        <v>4</v>
+      <c r="B223" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C223" s="0" t="s">
-        <v>1</v>
+        <v>314</v>
       </c>
       <c r="D223" s="0" t="s">
         <v>237</v>
@@ -4570,11 +5071,11 @@
       <c r="A224" s="0" t="s">
         <v>199</v>
       </c>
-      <c r="B224" s="0">
-        <v>4</v>
+      <c r="B224" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C224" s="0" t="s">
-        <v>1</v>
+        <v>314</v>
       </c>
       <c r="D224" s="0" t="s">
         <v>237</v>
@@ -4587,11 +5088,11 @@
       <c r="A225" s="0" t="s">
         <v>199</v>
       </c>
-      <c r="B225" s="0">
-        <v>4</v>
+      <c r="B225" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C225" s="0" t="s">
-        <v>1</v>
+        <v>314</v>
       </c>
       <c r="D225" s="0" t="s">
         <v>237</v>
@@ -4604,11 +5105,11 @@
       <c r="A226" s="0" t="s">
         <v>199</v>
       </c>
-      <c r="B226" s="0">
-        <v>4</v>
+      <c r="B226" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C226" s="0" t="s">
-        <v>1</v>
+        <v>314</v>
       </c>
       <c r="D226" s="0" t="s">
         <v>237</v>
@@ -4621,11 +5122,11 @@
       <c r="A227" s="0" t="s">
         <v>199</v>
       </c>
-      <c r="B227" s="0">
-        <v>4</v>
+      <c r="B227" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C227" s="0" t="s">
-        <v>1</v>
+        <v>314</v>
       </c>
       <c r="D227" s="0" t="s">
         <v>237</v>
@@ -4638,11 +5139,11 @@
       <c r="A228" s="0" t="s">
         <v>200</v>
       </c>
-      <c r="B228" s="0">
-        <v>2</v>
+      <c r="B228" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C228" s="0" t="s">
-        <v>1</v>
+        <v>315</v>
       </c>
       <c r="D228" s="0" t="s">
         <v>237</v>
@@ -4655,11 +5156,11 @@
       <c r="A229" s="0" t="s">
         <v>200</v>
       </c>
-      <c r="B229" s="0">
-        <v>2</v>
+      <c r="B229" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C229" s="0" t="s">
-        <v>1</v>
+        <v>315</v>
       </c>
       <c r="D229" s="0" t="s">
         <v>237</v>
@@ -4672,11 +5173,11 @@
       <c r="A230" s="0" t="s">
         <v>200</v>
       </c>
-      <c r="B230" s="0">
-        <v>2</v>
+      <c r="B230" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C230" s="0" t="s">
-        <v>1</v>
+        <v>315</v>
       </c>
       <c r="D230" s="0" t="s">
         <v>237</v>
@@ -4689,11 +5190,11 @@
       <c r="A231" s="0" t="s">
         <v>200</v>
       </c>
-      <c r="B231" s="0">
-        <v>3</v>
+      <c r="B231" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C231" s="0" t="s">
-        <v>1</v>
+        <v>316</v>
       </c>
       <c r="D231" s="0" t="s">
         <v>237</v>
@@ -4706,11 +5207,11 @@
       <c r="A232" s="0" t="s">
         <v>200</v>
       </c>
-      <c r="B232" s="0">
-        <v>4</v>
+      <c r="B232" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C232" s="0" t="s">
-        <v>1</v>
+        <v>317</v>
       </c>
       <c r="D232" s="0" t="s">
         <v>237</v>
@@ -4723,11 +5224,11 @@
       <c r="A233" s="0" t="s">
         <v>200</v>
       </c>
-      <c r="B233" s="0">
-        <v>4</v>
+      <c r="B233" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C233" s="0" t="s">
-        <v>1</v>
+        <v>317</v>
       </c>
       <c r="D233" s="0" t="s">
         <v>237</v>
@@ -4740,11 +5241,11 @@
       <c r="A234" s="0" t="s">
         <v>200</v>
       </c>
-      <c r="B234" s="0">
-        <v>4</v>
+      <c r="B234" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C234" s="0" t="s">
-        <v>1</v>
+        <v>317</v>
       </c>
       <c r="D234" s="0" t="s">
         <v>237</v>
@@ -4757,11 +5258,11 @@
       <c r="A235" s="0" t="s">
         <v>201</v>
       </c>
-      <c r="B235" s="0">
-        <v>2</v>
+      <c r="B235" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C235" s="0" t="s">
-        <v>1</v>
+        <v>318</v>
       </c>
       <c r="D235" s="0" t="s">
         <v>237</v>
@@ -4774,11 +5275,11 @@
       <c r="A236" s="0" t="s">
         <v>201</v>
       </c>
-      <c r="B236" s="0">
-        <v>4</v>
+      <c r="B236" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C236" s="0" t="s">
-        <v>1</v>
+        <v>319</v>
       </c>
       <c r="D236" s="0" t="s">
         <v>237</v>
@@ -4791,11 +5292,11 @@
       <c r="A237" s="0" t="s">
         <v>202</v>
       </c>
-      <c r="B237" s="0">
-        <v>3</v>
+      <c r="B237" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C237" s="0" t="s">
-        <v>1</v>
+        <v>320</v>
       </c>
       <c r="D237" s="0" t="s">
         <v>237</v>
@@ -4808,11 +5309,11 @@
       <c r="A238" s="0" t="s">
         <v>202</v>
       </c>
-      <c r="B238" s="0">
-        <v>3</v>
+      <c r="B238" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C238" s="0" t="s">
-        <v>1</v>
+        <v>320</v>
       </c>
       <c r="D238" s="0" t="s">
         <v>237</v>
@@ -4825,11 +5326,11 @@
       <c r="A239" s="0" t="s">
         <v>202</v>
       </c>
-      <c r="B239" s="0">
-        <v>3</v>
+      <c r="B239" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C239" s="0" t="s">
-        <v>1</v>
+        <v>320</v>
       </c>
       <c r="D239" s="0" t="s">
         <v>237</v>
@@ -4842,11 +5343,11 @@
       <c r="A240" s="0" t="s">
         <v>202</v>
       </c>
-      <c r="B240" s="0">
-        <v>3</v>
+      <c r="B240" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C240" s="0" t="s">
-        <v>1</v>
+        <v>320</v>
       </c>
       <c r="D240" s="0" t="s">
         <v>237</v>
@@ -4859,11 +5360,11 @@
       <c r="A241" s="0" t="s">
         <v>202</v>
       </c>
-      <c r="B241" s="0">
-        <v>3</v>
+      <c r="B241" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C241" s="0" t="s">
-        <v>1</v>
+        <v>320</v>
       </c>
       <c r="D241" s="0" t="s">
         <v>237</v>
@@ -4876,11 +5377,11 @@
       <c r="A242" s="0" t="s">
         <v>203</v>
       </c>
-      <c r="B242" s="0">
-        <v>1</v>
+      <c r="B242" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C242" s="0" t="s">
-        <v>1</v>
+        <v>321</v>
       </c>
       <c r="D242" s="0" t="s">
         <v>237</v>
@@ -4893,11 +5394,11 @@
       <c r="A243" s="0" t="s">
         <v>203</v>
       </c>
-      <c r="B243" s="0">
-        <v>1</v>
+      <c r="B243" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C243" s="0" t="s">
-        <v>1</v>
+        <v>321</v>
       </c>
       <c r="D243" s="0" t="s">
         <v>237</v>
@@ -4910,11 +5411,11 @@
       <c r="A244" s="0" t="s">
         <v>203</v>
       </c>
-      <c r="B244" s="0">
-        <v>2</v>
+      <c r="B244" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C244" s="0" t="s">
-        <v>1</v>
+        <v>322</v>
       </c>
       <c r="D244" s="0" t="s">
         <v>237</v>
@@ -4927,11 +5428,11 @@
       <c r="A245" s="0" t="s">
         <v>203</v>
       </c>
-      <c r="B245" s="0">
-        <v>3</v>
+      <c r="B245" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C245" s="0" t="s">
-        <v>1</v>
+        <v>323</v>
       </c>
       <c r="D245" s="0" t="s">
         <v>237</v>
@@ -4944,11 +5445,11 @@
       <c r="A246" s="0" t="s">
         <v>203</v>
       </c>
-      <c r="B246" s="0">
-        <v>4</v>
+      <c r="B246" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C246" s="0" t="s">
-        <v>1</v>
+        <v>324</v>
       </c>
       <c r="D246" s="0" t="s">
         <v>237</v>
@@ -4961,11 +5462,11 @@
       <c r="A247" s="0" t="s">
         <v>203</v>
       </c>
-      <c r="B247" s="0">
-        <v>4</v>
+      <c r="B247" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C247" s="0" t="s">
-        <v>1</v>
+        <v>324</v>
       </c>
       <c r="D247" s="0" t="s">
         <v>237</v>
@@ -4978,11 +5479,11 @@
       <c r="A248" s="0" t="s">
         <v>203</v>
       </c>
-      <c r="B248" s="0">
-        <v>4</v>
+      <c r="B248" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C248" s="0" t="s">
-        <v>1</v>
+        <v>324</v>
       </c>
       <c r="D248" s="0" t="s">
         <v>237</v>
@@ -4995,11 +5496,11 @@
       <c r="A249" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="B249" s="0">
-        <v>2</v>
+      <c r="B249" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C249" s="0" t="s">
-        <v>1</v>
+        <v>325</v>
       </c>
       <c r="D249" s="0" t="s">
         <v>237</v>
@@ -5012,11 +5513,11 @@
       <c r="A250" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="B250" s="0">
-        <v>3</v>
+      <c r="B250" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C250" s="0" t="s">
-        <v>1</v>
+        <v>326</v>
       </c>
       <c r="D250" s="0" t="s">
         <v>237</v>
@@ -5029,11 +5530,11 @@
       <c r="A251" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="B251" s="0">
-        <v>3</v>
+      <c r="B251" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C251" s="0" t="s">
-        <v>1</v>
+        <v>326</v>
       </c>
       <c r="D251" s="0" t="s">
         <v>237</v>
@@ -5046,11 +5547,11 @@
       <c r="A252" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="B252" s="0">
-        <v>3</v>
+      <c r="B252" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C252" s="0" t="s">
-        <v>1</v>
+        <v>326</v>
       </c>
       <c r="D252" s="0" t="s">
         <v>237</v>
@@ -5063,11 +5564,11 @@
       <c r="A253" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="B253" s="0">
-        <v>4</v>
+      <c r="B253" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C253" s="0" t="s">
-        <v>1</v>
+        <v>327</v>
       </c>
       <c r="D253" s="0" t="s">
         <v>237</v>
@@ -5080,11 +5581,11 @@
       <c r="A254" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="B254" s="0">
-        <v>4</v>
+      <c r="B254" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C254" s="0" t="s">
-        <v>1</v>
+        <v>327</v>
       </c>
       <c r="D254" s="0" t="s">
         <v>237</v>
@@ -5097,11 +5598,11 @@
       <c r="A255" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="B255" s="0">
-        <v>4</v>
+      <c r="B255" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C255" s="0" t="s">
-        <v>1</v>
+        <v>327</v>
       </c>
       <c r="D255" s="0" t="s">
         <v>237</v>
@@ -5114,11 +5615,11 @@
       <c r="A256" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="B256" s="0">
-        <v>4</v>
+      <c r="B256" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C256" s="0" t="s">
-        <v>1</v>
+        <v>327</v>
       </c>
       <c r="D256" s="0" t="s">
         <v>237</v>
@@ -5131,11 +5632,11 @@
       <c r="A257" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="B257" s="0">
-        <v>4</v>
+      <c r="B257" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C257" s="0" t="s">
-        <v>1</v>
+        <v>327</v>
       </c>
       <c r="D257" s="0" t="s">
         <v>237</v>
@@ -5148,11 +5649,11 @@
       <c r="A258" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="B258" s="0">
-        <v>4</v>
+      <c r="B258" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C258" s="0" t="s">
-        <v>1</v>
+        <v>327</v>
       </c>
       <c r="D258" s="0" t="s">
         <v>237</v>
@@ -5165,11 +5666,11 @@
       <c r="A259" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="B259" s="0">
-        <v>4</v>
+      <c r="B259" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C259" s="0" t="s">
-        <v>1</v>
+        <v>327</v>
       </c>
       <c r="D259" s="0" t="s">
         <v>237</v>
@@ -5182,11 +5683,11 @@
       <c r="A260" s="0" t="s">
         <v>205</v>
       </c>
-      <c r="B260" s="0">
-        <v>3</v>
+      <c r="B260" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C260" s="0" t="s">
-        <v>1</v>
+        <v>328</v>
       </c>
       <c r="D260" s="0" t="s">
         <v>237</v>
@@ -5199,11 +5700,11 @@
       <c r="A261" s="0" t="s">
         <v>205</v>
       </c>
-      <c r="B261" s="0">
-        <v>4</v>
+      <c r="B261" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C261" s="0" t="s">
-        <v>1</v>
+        <v>329</v>
       </c>
       <c r="D261" s="0" t="s">
         <v>237</v>
@@ -5216,11 +5717,11 @@
       <c r="A262" s="0" t="s">
         <v>206</v>
       </c>
-      <c r="B262" s="0">
-        <v>2</v>
+      <c r="B262" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C262" s="0" t="s">
-        <v>1</v>
+        <v>330</v>
       </c>
       <c r="D262" s="0" t="s">
         <v>237</v>
@@ -5233,11 +5734,11 @@
       <c r="A263" s="0" t="s">
         <v>206</v>
       </c>
-      <c r="B263" s="0">
-        <v>3</v>
+      <c r="B263" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C263" s="0" t="s">
-        <v>1</v>
+        <v>331</v>
       </c>
       <c r="D263" s="0" t="s">
         <v>237</v>
@@ -5250,11 +5751,11 @@
       <c r="A264" s="0" t="s">
         <v>207</v>
       </c>
-      <c r="B264" s="0">
-        <v>1</v>
+      <c r="B264" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C264" s="0" t="s">
-        <v>1</v>
+        <v>332</v>
       </c>
       <c r="D264" s="0" t="s">
         <v>237</v>
@@ -5267,11 +5768,11 @@
       <c r="A265" s="0" t="s">
         <v>207</v>
       </c>
-      <c r="B265" s="0">
-        <v>1</v>
+      <c r="B265" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C265" s="0" t="s">
-        <v>1</v>
+        <v>332</v>
       </c>
       <c r="D265" s="0" t="s">
         <v>237</v>
@@ -5284,11 +5785,11 @@
       <c r="A266" s="0" t="s">
         <v>207</v>
       </c>
-      <c r="B266" s="0">
-        <v>1</v>
+      <c r="B266" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C266" s="0" t="s">
-        <v>1</v>
+        <v>332</v>
       </c>
       <c r="D266" s="0" t="s">
         <v>237</v>
@@ -5301,11 +5802,11 @@
       <c r="A267" s="0" t="s">
         <v>207</v>
       </c>
-      <c r="B267" s="0">
-        <v>2</v>
+      <c r="B267" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C267" s="0" t="s">
-        <v>1</v>
+        <v>333</v>
       </c>
       <c r="D267" s="0" t="s">
         <v>237</v>
@@ -5318,11 +5819,11 @@
       <c r="A268" s="0" t="s">
         <v>207</v>
       </c>
-      <c r="B268" s="0">
-        <v>2</v>
+      <c r="B268" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C268" s="0" t="s">
-        <v>1</v>
+        <v>333</v>
       </c>
       <c r="D268" s="0" t="s">
         <v>237</v>
@@ -5335,11 +5836,11 @@
       <c r="A269" s="0" t="s">
         <v>207</v>
       </c>
-      <c r="B269" s="0">
-        <v>4</v>
+      <c r="B269" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C269" s="0" t="s">
-        <v>1</v>
+        <v>334</v>
       </c>
       <c r="D269" s="0" t="s">
         <v>237</v>
@@ -5352,11 +5853,11 @@
       <c r="A270" s="0" t="s">
         <v>207</v>
       </c>
-      <c r="B270" s="0">
-        <v>4</v>
+      <c r="B270" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C270" s="0" t="s">
-        <v>1</v>
+        <v>334</v>
       </c>
       <c r="D270" s="0" t="s">
         <v>237</v>
@@ -5369,11 +5870,11 @@
       <c r="A271" s="0" t="s">
         <v>207</v>
       </c>
-      <c r="B271" s="0">
-        <v>4</v>
+      <c r="B271" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C271" s="0" t="s">
-        <v>1</v>
+        <v>334</v>
       </c>
       <c r="D271" s="0" t="s">
         <v>237</v>
@@ -5386,11 +5887,11 @@
       <c r="A272" s="0" t="s">
         <v>207</v>
       </c>
-      <c r="B272" s="0">
-        <v>4</v>
+      <c r="B272" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C272" s="0" t="s">
-        <v>1</v>
+        <v>334</v>
       </c>
       <c r="D272" s="0" t="s">
         <v>237</v>
@@ -5403,11 +5904,11 @@
       <c r="A273" s="0" t="s">
         <v>207</v>
       </c>
-      <c r="B273" s="0">
-        <v>4</v>
+      <c r="B273" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C273" s="0" t="s">
-        <v>1</v>
+        <v>334</v>
       </c>
       <c r="D273" s="0" t="s">
         <v>237</v>
@@ -5420,11 +5921,11 @@
       <c r="A274" s="0" t="s">
         <v>208</v>
       </c>
-      <c r="B274" s="0">
-        <v>2</v>
+      <c r="B274" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C274" s="0" t="s">
-        <v>1</v>
+        <v>335</v>
       </c>
       <c r="D274" s="0" t="s">
         <v>237</v>
@@ -5437,11 +5938,11 @@
       <c r="A275" s="0" t="s">
         <v>208</v>
       </c>
-      <c r="B275" s="0">
-        <v>2</v>
+      <c r="B275" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C275" s="0" t="s">
-        <v>1</v>
+        <v>335</v>
       </c>
       <c r="D275" s="0" t="s">
         <v>237</v>
@@ -5454,11 +5955,11 @@
       <c r="A276" s="0" t="s">
         <v>208</v>
       </c>
-      <c r="B276" s="0">
-        <v>4</v>
+      <c r="B276" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C276" s="0" t="s">
-        <v>1</v>
+        <v>336</v>
       </c>
       <c r="D276" s="0" t="s">
         <v>237</v>
@@ -5471,11 +5972,11 @@
       <c r="A277" s="0" t="s">
         <v>208</v>
       </c>
-      <c r="B277" s="0">
-        <v>4</v>
+      <c r="B277" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C277" s="0" t="s">
-        <v>1</v>
+        <v>336</v>
       </c>
       <c r="D277" s="0" t="s">
         <v>237</v>
@@ -5488,11 +5989,11 @@
       <c r="A278" s="0" t="s">
         <v>208</v>
       </c>
-      <c r="B278" s="0">
-        <v>4</v>
+      <c r="B278" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C278" s="0" t="s">
-        <v>1</v>
+        <v>336</v>
       </c>
       <c r="D278" s="0" t="s">
         <v>237</v>
@@ -5505,11 +6006,11 @@
       <c r="A279" s="0" t="s">
         <v>208</v>
       </c>
-      <c r="B279" s="0">
-        <v>4</v>
+      <c r="B279" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C279" s="0" t="s">
-        <v>1</v>
+        <v>336</v>
       </c>
       <c r="D279" s="0" t="s">
         <v>237</v>
@@ -5522,11 +6023,11 @@
       <c r="A280" s="0" t="s">
         <v>208</v>
       </c>
-      <c r="B280" s="0">
-        <v>4</v>
+      <c r="B280" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C280" s="0" t="s">
-        <v>1</v>
+        <v>336</v>
       </c>
       <c r="D280" s="0" t="s">
         <v>237</v>
@@ -5539,11 +6040,11 @@
       <c r="A281" s="0" t="s">
         <v>208</v>
       </c>
-      <c r="B281" s="0">
-        <v>4</v>
+      <c r="B281" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C281" s="0" t="s">
-        <v>1</v>
+        <v>336</v>
       </c>
       <c r="D281" s="0" t="s">
         <v>237</v>
@@ -5556,11 +6057,11 @@
       <c r="A282" s="0" t="s">
         <v>208</v>
       </c>
-      <c r="B282" s="0">
-        <v>4</v>
+      <c r="B282" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C282" s="0" t="s">
-        <v>1</v>
+        <v>336</v>
       </c>
       <c r="D282" s="0" t="s">
         <v>237</v>
@@ -5573,11 +6074,11 @@
       <c r="A283" s="0" t="s">
         <v>209</v>
       </c>
-      <c r="B283" s="0">
-        <v>2</v>
+      <c r="B283" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C283" s="0" t="s">
-        <v>1</v>
+        <v>337</v>
       </c>
       <c r="D283" s="0" t="s">
         <v>237</v>
@@ -5590,11 +6091,11 @@
       <c r="A284" s="0" t="s">
         <v>209</v>
       </c>
-      <c r="B284" s="0">
-        <v>2</v>
+      <c r="B284" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C284" s="0" t="s">
-        <v>1</v>
+        <v>337</v>
       </c>
       <c r="D284" s="0" t="s">
         <v>237</v>
@@ -5607,11 +6108,11 @@
       <c r="A285" s="0" t="s">
         <v>209</v>
       </c>
-      <c r="B285" s="0">
-        <v>2</v>
+      <c r="B285" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C285" s="0" t="s">
-        <v>1</v>
+        <v>337</v>
       </c>
       <c r="D285" s="0" t="s">
         <v>237</v>
@@ -5624,11 +6125,11 @@
       <c r="A286" s="0" t="s">
         <v>209</v>
       </c>
-      <c r="B286" s="0">
-        <v>2</v>
+      <c r="B286" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C286" s="0" t="s">
-        <v>1</v>
+        <v>337</v>
       </c>
       <c r="D286" s="0" t="s">
         <v>237</v>
@@ -5641,11 +6142,11 @@
       <c r="A287" s="0" t="s">
         <v>209</v>
       </c>
-      <c r="B287" s="0">
-        <v>2</v>
+      <c r="B287" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C287" s="0" t="s">
-        <v>1</v>
+        <v>337</v>
       </c>
       <c r="D287" s="0" t="s">
         <v>237</v>
@@ -5658,11 +6159,11 @@
       <c r="A288" s="0" t="s">
         <v>209</v>
       </c>
-      <c r="B288" s="0">
-        <v>2</v>
+      <c r="B288" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C288" s="0" t="s">
-        <v>1</v>
+        <v>337</v>
       </c>
       <c r="D288" s="0" t="s">
         <v>237</v>
@@ -5675,11 +6176,11 @@
       <c r="A289" s="0" t="s">
         <v>209</v>
       </c>
-      <c r="B289" s="0">
-        <v>3</v>
+      <c r="B289" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C289" s="0" t="s">
-        <v>1</v>
+        <v>338</v>
       </c>
       <c r="D289" s="0" t="s">
         <v>237</v>
@@ -5692,11 +6193,11 @@
       <c r="A290" s="0" t="s">
         <v>210</v>
       </c>
-      <c r="B290" s="0">
-        <v>2</v>
+      <c r="B290" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C290" s="0" t="s">
-        <v>1</v>
+        <v>339</v>
       </c>
       <c r="D290" s="0" t="s">
         <v>237</v>
@@ -5709,11 +6210,11 @@
       <c r="A291" s="0" t="s">
         <v>210</v>
       </c>
-      <c r="B291" s="0">
-        <v>2</v>
+      <c r="B291" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C291" s="0" t="s">
-        <v>1</v>
+        <v>339</v>
       </c>
       <c r="D291" s="0" t="s">
         <v>237</v>
@@ -5726,11 +6227,11 @@
       <c r="A292" s="0" t="s">
         <v>211</v>
       </c>
-      <c r="B292" s="0">
-        <v>1</v>
+      <c r="B292" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C292" s="0" t="s">
-        <v>1</v>
+        <v>340</v>
       </c>
       <c r="D292" s="0" t="s">
         <v>237</v>
@@ -5743,11 +6244,11 @@
       <c r="A293" s="0" t="s">
         <v>211</v>
       </c>
-      <c r="B293" s="0">
-        <v>1</v>
+      <c r="B293" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C293" s="0" t="s">
-        <v>1</v>
+        <v>340</v>
       </c>
       <c r="D293" s="0" t="s">
         <v>237</v>
@@ -5760,11 +6261,11 @@
       <c r="A294" s="0" t="s">
         <v>211</v>
       </c>
-      <c r="B294" s="0">
-        <v>1</v>
+      <c r="B294" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C294" s="0" t="s">
-        <v>1</v>
+        <v>340</v>
       </c>
       <c r="D294" s="0" t="s">
         <v>237</v>
@@ -5777,11 +6278,11 @@
       <c r="A295" s="0" t="s">
         <v>211</v>
       </c>
-      <c r="B295" s="0">
-        <v>1</v>
+      <c r="B295" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C295" s="0" t="s">
-        <v>1</v>
+        <v>340</v>
       </c>
       <c r="D295" s="0" t="s">
         <v>237</v>
@@ -5794,11 +6295,11 @@
       <c r="A296" s="0" t="s">
         <v>211</v>
       </c>
-      <c r="B296" s="0">
-        <v>1</v>
+      <c r="B296" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C296" s="0" t="s">
-        <v>1</v>
+        <v>340</v>
       </c>
       <c r="D296" s="0" t="s">
         <v>237</v>
@@ -5811,11 +6312,11 @@
       <c r="A297" s="0" t="s">
         <v>211</v>
       </c>
-      <c r="B297" s="0">
-        <v>1</v>
+      <c r="B297" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C297" s="0" t="s">
-        <v>1</v>
+        <v>340</v>
       </c>
       <c r="D297" s="0" t="s">
         <v>237</v>
@@ -5828,11 +6329,11 @@
       <c r="A298" s="0" t="s">
         <v>211</v>
       </c>
-      <c r="B298" s="0">
-        <v>2</v>
+      <c r="B298" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C298" s="0" t="s">
-        <v>1</v>
+        <v>341</v>
       </c>
       <c r="D298" s="0" t="s">
         <v>237</v>
@@ -5845,11 +6346,11 @@
       <c r="A299" s="0" t="s">
         <v>211</v>
       </c>
-      <c r="B299" s="0">
-        <v>2</v>
+      <c r="B299" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C299" s="0" t="s">
-        <v>1</v>
+        <v>341</v>
       </c>
       <c r="D299" s="0" t="s">
         <v>237</v>
@@ -5862,11 +6363,11 @@
       <c r="A300" s="0" t="s">
         <v>211</v>
       </c>
-      <c r="B300" s="0">
-        <v>2</v>
+      <c r="B300" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C300" s="0" t="s">
-        <v>1</v>
+        <v>341</v>
       </c>
       <c r="D300" s="0" t="s">
         <v>237</v>
@@ -5879,11 +6380,11 @@
       <c r="A301" s="0" t="s">
         <v>211</v>
       </c>
-      <c r="B301" s="0">
-        <v>2</v>
+      <c r="B301" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C301" s="0" t="s">
-        <v>1</v>
+        <v>341</v>
       </c>
       <c r="D301" s="0" t="s">
         <v>237</v>
@@ -5896,11 +6397,11 @@
       <c r="A302" s="0" t="s">
         <v>211</v>
       </c>
-      <c r="B302" s="0">
-        <v>2</v>
+      <c r="B302" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C302" s="0" t="s">
-        <v>1</v>
+        <v>341</v>
       </c>
       <c r="D302" s="0" t="s">
         <v>237</v>
@@ -5913,11 +6414,11 @@
       <c r="A303" s="0" t="s">
         <v>211</v>
       </c>
-      <c r="B303" s="0">
-        <v>2</v>
+      <c r="B303" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C303" s="0" t="s">
-        <v>1</v>
+        <v>341</v>
       </c>
       <c r="D303" s="0" t="s">
         <v>237</v>
@@ -5930,11 +6431,11 @@
       <c r="A304" s="0" t="s">
         <v>211</v>
       </c>
-      <c r="B304" s="0">
-        <v>2</v>
+      <c r="B304" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C304" s="0" t="s">
-        <v>1</v>
+        <v>341</v>
       </c>
       <c r="D304" s="0" t="s">
         <v>237</v>
@@ -5947,11 +6448,11 @@
       <c r="A305" s="0" t="s">
         <v>211</v>
       </c>
-      <c r="B305" s="0">
-        <v>3</v>
+      <c r="B305" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C305" s="0" t="s">
-        <v>1</v>
+        <v>342</v>
       </c>
       <c r="D305" s="0" t="s">
         <v>237</v>
@@ -5964,11 +6465,11 @@
       <c r="A306" s="0" t="s">
         <v>211</v>
       </c>
-      <c r="B306" s="0">
-        <v>3</v>
+      <c r="B306" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C306" s="0" t="s">
-        <v>1</v>
+        <v>342</v>
       </c>
       <c r="D306" s="0" t="s">
         <v>237</v>
@@ -5981,11 +6482,11 @@
       <c r="A307" s="0" t="s">
         <v>211</v>
       </c>
-      <c r="B307" s="0">
-        <v>3</v>
+      <c r="B307" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C307" s="0" t="s">
-        <v>1</v>
+        <v>342</v>
       </c>
       <c r="D307" s="0" t="s">
         <v>237</v>
@@ -5998,11 +6499,11 @@
       <c r="A308" s="0" t="s">
         <v>211</v>
       </c>
-      <c r="B308" s="0">
-        <v>3</v>
+      <c r="B308" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C308" s="0" t="s">
-        <v>1</v>
+        <v>342</v>
       </c>
       <c r="D308" s="0" t="s">
         <v>237</v>
@@ -6015,11 +6516,11 @@
       <c r="A309" s="0" t="s">
         <v>211</v>
       </c>
-      <c r="B309" s="0">
-        <v>3</v>
+      <c r="B309" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C309" s="0" t="s">
-        <v>1</v>
+        <v>342</v>
       </c>
       <c r="D309" s="0" t="s">
         <v>237</v>
@@ -6032,11 +6533,11 @@
       <c r="A310" s="0" t="s">
         <v>211</v>
       </c>
-      <c r="B310" s="0">
-        <v>4</v>
+      <c r="B310" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C310" s="0" t="s">
-        <v>1</v>
+        <v>343</v>
       </c>
       <c r="D310" s="0" t="s">
         <v>237</v>
@@ -6049,11 +6550,11 @@
       <c r="A311" s="0" t="s">
         <v>211</v>
       </c>
-      <c r="B311" s="0">
-        <v>4</v>
+      <c r="B311" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C311" s="0" t="s">
-        <v>1</v>
+        <v>343</v>
       </c>
       <c r="D311" s="0" t="s">
         <v>237</v>
@@ -6066,11 +6567,11 @@
       <c r="A312" s="0" t="s">
         <v>211</v>
       </c>
-      <c r="B312" s="0">
-        <v>4</v>
+      <c r="B312" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C312" s="0" t="s">
-        <v>1</v>
+        <v>343</v>
       </c>
       <c r="D312" s="0" t="s">
         <v>237</v>
@@ -6083,11 +6584,11 @@
       <c r="A313" s="0" t="s">
         <v>211</v>
       </c>
-      <c r="B313" s="0">
-        <v>4</v>
+      <c r="B313" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C313" s="0" t="s">
-        <v>1</v>
+        <v>343</v>
       </c>
       <c r="D313" s="0" t="s">
         <v>237</v>
@@ -6100,11 +6601,11 @@
       <c r="A314" s="0" t="s">
         <v>211</v>
       </c>
-      <c r="B314" s="0">
-        <v>4</v>
+      <c r="B314" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C314" s="0" t="s">
-        <v>1</v>
+        <v>343</v>
       </c>
       <c r="D314" s="0" t="s">
         <v>237</v>
@@ -6117,11 +6618,11 @@
       <c r="A315" s="0" t="s">
         <v>211</v>
       </c>
-      <c r="B315" s="0">
-        <v>4</v>
+      <c r="B315" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C315" s="0" t="s">
-        <v>1</v>
+        <v>343</v>
       </c>
       <c r="D315" s="0" t="s">
         <v>237</v>
@@ -6134,11 +6635,11 @@
       <c r="A316" s="0" t="s">
         <v>211</v>
       </c>
-      <c r="B316" s="0">
-        <v>4</v>
+      <c r="B316" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C316" s="0" t="s">
-        <v>1</v>
+        <v>343</v>
       </c>
       <c r="D316" s="0" t="s">
         <v>237</v>
@@ -6151,11 +6652,11 @@
       <c r="A317" s="0" t="s">
         <v>211</v>
       </c>
-      <c r="B317" s="0">
-        <v>4</v>
+      <c r="B317" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C317" s="0" t="s">
-        <v>1</v>
+        <v>343</v>
       </c>
       <c r="D317" s="0" t="s">
         <v>237</v>
@@ -6168,11 +6669,11 @@
       <c r="A318" s="0" t="s">
         <v>212</v>
       </c>
-      <c r="B318" s="0">
-        <v>1</v>
+      <c r="B318" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C318" s="0" t="s">
-        <v>1</v>
+        <v>344</v>
       </c>
       <c r="D318" s="0" t="s">
         <v>237</v>
@@ -6185,11 +6686,11 @@
       <c r="A319" s="0" t="s">
         <v>212</v>
       </c>
-      <c r="B319" s="0">
-        <v>2</v>
+      <c r="B319" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C319" s="0" t="s">
-        <v>1</v>
+        <v>345</v>
       </c>
       <c r="D319" s="0" t="s">
         <v>237</v>
@@ -6202,11 +6703,11 @@
       <c r="A320" s="0" t="s">
         <v>213</v>
       </c>
-      <c r="B320" s="0">
-        <v>1</v>
+      <c r="B320" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C320" s="0" t="s">
-        <v>1</v>
+        <v>346</v>
       </c>
       <c r="D320" s="0" t="s">
         <v>237</v>
@@ -6219,11 +6720,11 @@
       <c r="A321" s="0" t="s">
         <v>213</v>
       </c>
-      <c r="B321" s="0">
-        <v>1</v>
+      <c r="B321" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C321" s="0" t="s">
-        <v>1</v>
+        <v>346</v>
       </c>
       <c r="D321" s="0" t="s">
         <v>237</v>
@@ -6236,11 +6737,11 @@
       <c r="A322" s="0" t="s">
         <v>213</v>
       </c>
-      <c r="B322" s="0">
-        <v>1</v>
+      <c r="B322" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C322" s="0" t="s">
-        <v>1</v>
+        <v>346</v>
       </c>
       <c r="D322" s="0" t="s">
         <v>237</v>
@@ -6253,11 +6754,11 @@
       <c r="A323" s="0" t="s">
         <v>213</v>
       </c>
-      <c r="B323" s="0">
-        <v>1</v>
+      <c r="B323" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C323" s="0" t="s">
-        <v>1</v>
+        <v>346</v>
       </c>
       <c r="D323" s="0" t="s">
         <v>237</v>
@@ -6270,11 +6771,11 @@
       <c r="A324" s="0" t="s">
         <v>213</v>
       </c>
-      <c r="B324" s="0">
-        <v>1</v>
+      <c r="B324" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C324" s="0" t="s">
-        <v>1</v>
+        <v>346</v>
       </c>
       <c r="D324" s="0" t="s">
         <v>237</v>
@@ -6287,11 +6788,11 @@
       <c r="A325" s="0" t="s">
         <v>213</v>
       </c>
-      <c r="B325" s="0">
-        <v>2</v>
+      <c r="B325" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C325" s="0" t="s">
-        <v>1</v>
+        <v>347</v>
       </c>
       <c r="D325" s="0" t="s">
         <v>237</v>
@@ -6304,11 +6805,11 @@
       <c r="A326" s="0" t="s">
         <v>213</v>
       </c>
-      <c r="B326" s="0">
-        <v>2</v>
+      <c r="B326" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C326" s="0" t="s">
-        <v>1</v>
+        <v>347</v>
       </c>
       <c r="D326" s="0" t="s">
         <v>237</v>
@@ -6321,11 +6822,11 @@
       <c r="A327" s="0" t="s">
         <v>213</v>
       </c>
-      <c r="B327" s="0">
-        <v>2</v>
+      <c r="B327" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C327" s="0" t="s">
-        <v>1</v>
+        <v>347</v>
       </c>
       <c r="D327" s="0" t="s">
         <v>237</v>
@@ -6338,11 +6839,11 @@
       <c r="A328" s="0" t="s">
         <v>213</v>
       </c>
-      <c r="B328" s="0">
-        <v>2</v>
+      <c r="B328" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C328" s="0" t="s">
-        <v>1</v>
+        <v>347</v>
       </c>
       <c r="D328" s="0" t="s">
         <v>237</v>
@@ -6355,11 +6856,11 @@
       <c r="A329" s="0" t="s">
         <v>213</v>
       </c>
-      <c r="B329" s="0">
-        <v>2</v>
+      <c r="B329" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C329" s="0" t="s">
-        <v>1</v>
+        <v>347</v>
       </c>
       <c r="D329" s="0" t="s">
         <v>237</v>
@@ -6372,11 +6873,11 @@
       <c r="A330" s="0" t="s">
         <v>213</v>
       </c>
-      <c r="B330" s="0">
-        <v>4</v>
+      <c r="B330" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C330" s="0" t="s">
-        <v>1</v>
+        <v>348</v>
       </c>
       <c r="D330" s="0" t="s">
         <v>237</v>
@@ -6389,11 +6890,11 @@
       <c r="A331" s="0" t="s">
         <v>213</v>
       </c>
-      <c r="B331" s="0">
-        <v>4</v>
+      <c r="B331" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C331" s="0" t="s">
-        <v>1</v>
+        <v>348</v>
       </c>
       <c r="D331" s="0" t="s">
         <v>237</v>
@@ -6406,11 +6907,11 @@
       <c r="A332" s="0" t="s">
         <v>213</v>
       </c>
-      <c r="B332" s="0">
-        <v>4</v>
+      <c r="B332" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C332" s="0" t="s">
-        <v>1</v>
+        <v>348</v>
       </c>
       <c r="D332" s="0" t="s">
         <v>237</v>
@@ -6423,11 +6924,11 @@
       <c r="A333" s="0" t="s">
         <v>213</v>
       </c>
-      <c r="B333" s="0">
-        <v>4</v>
+      <c r="B333" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C333" s="0" t="s">
-        <v>1</v>
+        <v>348</v>
       </c>
       <c r="D333" s="0" t="s">
         <v>237</v>
@@ -6440,11 +6941,11 @@
       <c r="A334" s="0" t="s">
         <v>213</v>
       </c>
-      <c r="B334" s="0">
-        <v>4</v>
+      <c r="B334" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C334" s="0" t="s">
-        <v>1</v>
+        <v>348</v>
       </c>
       <c r="D334" s="0" t="s">
         <v>237</v>
@@ -6457,11 +6958,11 @@
       <c r="A335" s="0" t="s">
         <v>213</v>
       </c>
-      <c r="B335" s="0">
-        <v>4</v>
+      <c r="B335" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C335" s="0" t="s">
-        <v>1</v>
+        <v>348</v>
       </c>
       <c r="D335" s="0" t="s">
         <v>237</v>
@@ -6474,11 +6975,11 @@
       <c r="A336" s="0" t="s">
         <v>214</v>
       </c>
-      <c r="B336" s="0">
-        <v>1</v>
+      <c r="B336" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C336" s="0" t="s">
-        <v>1</v>
+        <v>349</v>
       </c>
       <c r="D336" s="0" t="s">
         <v>237</v>
@@ -6491,11 +6992,11 @@
       <c r="A337" s="0" t="s">
         <v>214</v>
       </c>
-      <c r="B337" s="0">
-        <v>3</v>
+      <c r="B337" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C337" s="0" t="s">
-        <v>1</v>
+        <v>350</v>
       </c>
       <c r="D337" s="0" t="s">
         <v>237</v>
@@ -6508,11 +7009,11 @@
       <c r="A338" s="0" t="s">
         <v>214</v>
       </c>
-      <c r="B338" s="0">
-        <v>4</v>
+      <c r="B338" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C338" s="0" t="s">
-        <v>1</v>
+        <v>351</v>
       </c>
       <c r="D338" s="0" t="s">
         <v>237</v>
@@ -6525,11 +7026,11 @@
       <c r="A339" s="0" t="s">
         <v>214</v>
       </c>
-      <c r="B339" s="0">
-        <v>4</v>
+      <c r="B339" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C339" s="0" t="s">
-        <v>1</v>
+        <v>351</v>
       </c>
       <c r="D339" s="0" t="s">
         <v>237</v>
@@ -6542,11 +7043,11 @@
       <c r="A340" s="0" t="s">
         <v>214</v>
       </c>
-      <c r="B340" s="0">
-        <v>4</v>
+      <c r="B340" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C340" s="0" t="s">
-        <v>1</v>
+        <v>351</v>
       </c>
       <c r="D340" s="0" t="s">
         <v>237</v>
@@ -6559,11 +7060,11 @@
       <c r="A341" s="0" t="s">
         <v>215</v>
       </c>
-      <c r="B341" s="0">
-        <v>1</v>
+      <c r="B341" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C341" s="0" t="s">
-        <v>1</v>
+        <v>352</v>
       </c>
       <c r="D341" s="0" t="s">
         <v>237</v>
@@ -6576,11 +7077,11 @@
       <c r="A342" s="0" t="s">
         <v>215</v>
       </c>
-      <c r="B342" s="0">
-        <v>1</v>
+      <c r="B342" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C342" s="0" t="s">
-        <v>1</v>
+        <v>352</v>
       </c>
       <c r="D342" s="0" t="s">
         <v>237</v>
@@ -6593,11 +7094,11 @@
       <c r="A343" s="0" t="s">
         <v>215</v>
       </c>
-      <c r="B343" s="0">
-        <v>1</v>
+      <c r="B343" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C343" s="0" t="s">
-        <v>1</v>
+        <v>352</v>
       </c>
       <c r="D343" s="0" t="s">
         <v>237</v>
@@ -6610,11 +7111,11 @@
       <c r="A344" s="0" t="s">
         <v>215</v>
       </c>
-      <c r="B344" s="0">
-        <v>1</v>
+      <c r="B344" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C344" s="0" t="s">
-        <v>1</v>
+        <v>352</v>
       </c>
       <c r="D344" s="0" t="s">
         <v>237</v>
@@ -6627,11 +7128,11 @@
       <c r="A345" s="0" t="s">
         <v>215</v>
       </c>
-      <c r="B345" s="0">
-        <v>3</v>
+      <c r="B345" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C345" s="0" t="s">
-        <v>1</v>
+        <v>353</v>
       </c>
       <c r="D345" s="0" t="s">
         <v>237</v>
@@ -6644,11 +7145,11 @@
       <c r="A346" s="0" t="s">
         <v>215</v>
       </c>
-      <c r="B346" s="0">
-        <v>3</v>
+      <c r="B346" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C346" s="0" t="s">
-        <v>1</v>
+        <v>353</v>
       </c>
       <c r="D346" s="0" t="s">
         <v>237</v>
@@ -6661,11 +7162,11 @@
       <c r="A347" s="0" t="s">
         <v>215</v>
       </c>
-      <c r="B347" s="0">
-        <v>3</v>
+      <c r="B347" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C347" s="0" t="s">
-        <v>1</v>
+        <v>353</v>
       </c>
       <c r="D347" s="0" t="s">
         <v>237</v>
@@ -6678,11 +7179,11 @@
       <c r="A348" s="0" t="s">
         <v>215</v>
       </c>
-      <c r="B348" s="0">
-        <v>4</v>
+      <c r="B348" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C348" s="0" t="s">
-        <v>1</v>
+        <v>354</v>
       </c>
       <c r="D348" s="0" t="s">
         <v>237</v>
@@ -6695,11 +7196,11 @@
       <c r="A349" s="0" t="s">
         <v>216</v>
       </c>
-      <c r="B349" s="0">
-        <v>1</v>
+      <c r="B349" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C349" s="0" t="s">
-        <v>1</v>
+        <v>355</v>
       </c>
       <c r="D349" s="0" t="s">
         <v>237</v>
@@ -6712,11 +7213,11 @@
       <c r="A350" s="0" t="s">
         <v>216</v>
       </c>
-      <c r="B350" s="0">
-        <v>1</v>
+      <c r="B350" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C350" s="0" t="s">
-        <v>1</v>
+        <v>355</v>
       </c>
       <c r="D350" s="0" t="s">
         <v>237</v>
@@ -6729,11 +7230,11 @@
       <c r="A351" s="0" t="s">
         <v>216</v>
       </c>
-      <c r="B351" s="0">
-        <v>1</v>
+      <c r="B351" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C351" s="0" t="s">
-        <v>1</v>
+        <v>355</v>
       </c>
       <c r="D351" s="0" t="s">
         <v>237</v>
@@ -6746,11 +7247,11 @@
       <c r="A352" s="0" t="s">
         <v>216</v>
       </c>
-      <c r="B352" s="0">
-        <v>2</v>
+      <c r="B352" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C352" s="0" t="s">
-        <v>1</v>
+        <v>356</v>
       </c>
       <c r="D352" s="0" t="s">
         <v>237</v>
@@ -6763,11 +7264,11 @@
       <c r="A353" s="0" t="s">
         <v>216</v>
       </c>
-      <c r="B353" s="0">
-        <v>3</v>
+      <c r="B353" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C353" s="0" t="s">
-        <v>1</v>
+        <v>357</v>
       </c>
       <c r="D353" s="0" t="s">
         <v>237</v>
@@ -6780,11 +7281,11 @@
       <c r="A354" s="0" t="s">
         <v>216</v>
       </c>
-      <c r="B354" s="0">
-        <v>3</v>
+      <c r="B354" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C354" s="0" t="s">
-        <v>1</v>
+        <v>357</v>
       </c>
       <c r="D354" s="0" t="s">
         <v>237</v>
@@ -6797,11 +7298,11 @@
       <c r="A355" s="0" t="s">
         <v>216</v>
       </c>
-      <c r="B355" s="0">
-        <v>3</v>
+      <c r="B355" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C355" s="0" t="s">
-        <v>1</v>
+        <v>357</v>
       </c>
       <c r="D355" s="0" t="s">
         <v>237</v>
@@ -6814,11 +7315,11 @@
       <c r="A356" s="0" t="s">
         <v>216</v>
       </c>
-      <c r="B356" s="0">
-        <v>3</v>
+      <c r="B356" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C356" s="0" t="s">
-        <v>1</v>
+        <v>357</v>
       </c>
       <c r="D356" s="0" t="s">
         <v>237</v>
@@ -6831,11 +7332,11 @@
       <c r="A357" s="0" t="s">
         <v>216</v>
       </c>
-      <c r="B357" s="0">
-        <v>3</v>
+      <c r="B357" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C357" s="0" t="s">
-        <v>1</v>
+        <v>357</v>
       </c>
       <c r="D357" s="0" t="s">
         <v>237</v>
@@ -6848,11 +7349,11 @@
       <c r="A358" s="0" t="s">
         <v>216</v>
       </c>
-      <c r="B358" s="0">
-        <v>3</v>
+      <c r="B358" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C358" s="0" t="s">
-        <v>1</v>
+        <v>357</v>
       </c>
       <c r="D358" s="0" t="s">
         <v>237</v>
@@ -6865,11 +7366,11 @@
       <c r="A359" s="0" t="s">
         <v>216</v>
       </c>
-      <c r="B359" s="0">
-        <v>3</v>
+      <c r="B359" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C359" s="0" t="s">
-        <v>1</v>
+        <v>357</v>
       </c>
       <c r="D359" s="0" t="s">
         <v>237</v>
@@ -6882,11 +7383,11 @@
       <c r="A360" s="0" t="s">
         <v>216</v>
       </c>
-      <c r="B360" s="0">
-        <v>4</v>
+      <c r="B360" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C360" s="0" t="s">
-        <v>1</v>
+        <v>358</v>
       </c>
       <c r="D360" s="0" t="s">
         <v>237</v>
@@ -6899,11 +7400,11 @@
       <c r="A361" s="0" t="s">
         <v>216</v>
       </c>
-      <c r="B361" s="0">
-        <v>4</v>
+      <c r="B361" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C361" s="0" t="s">
-        <v>1</v>
+        <v>358</v>
       </c>
       <c r="D361" s="0" t="s">
         <v>237</v>
@@ -6916,11 +7417,11 @@
       <c r="A362" s="0" t="s">
         <v>216</v>
       </c>
-      <c r="B362" s="0">
-        <v>4</v>
+      <c r="B362" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C362" s="0" t="s">
-        <v>1</v>
+        <v>358</v>
       </c>
       <c r="D362" s="0" t="s">
         <v>237</v>
@@ -6933,11 +7434,11 @@
       <c r="A363" s="0" t="s">
         <v>216</v>
       </c>
-      <c r="B363" s="0">
-        <v>4</v>
+      <c r="B363" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C363" s="0" t="s">
-        <v>1</v>
+        <v>358</v>
       </c>
       <c r="D363" s="0" t="s">
         <v>237</v>
@@ -6950,11 +7451,11 @@
       <c r="A364" s="0" t="s">
         <v>216</v>
       </c>
-      <c r="B364" s="0">
-        <v>4</v>
+      <c r="B364" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C364" s="0" t="s">
-        <v>1</v>
+        <v>358</v>
       </c>
       <c r="D364" s="0" t="s">
         <v>237</v>
@@ -6967,11 +7468,11 @@
       <c r="A365" s="0" t="s">
         <v>217</v>
       </c>
-      <c r="B365" s="0">
-        <v>1</v>
+      <c r="B365" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C365" s="0" t="s">
-        <v>1</v>
+        <v>359</v>
       </c>
       <c r="D365" s="0" t="s">
         <v>237</v>
@@ -6984,11 +7485,11 @@
       <c r="A366" s="0" t="s">
         <v>217</v>
       </c>
-      <c r="B366" s="0">
-        <v>1</v>
+      <c r="B366" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C366" s="0" t="s">
-        <v>1</v>
+        <v>359</v>
       </c>
       <c r="D366" s="0" t="s">
         <v>237</v>
@@ -7001,11 +7502,11 @@
       <c r="A367" s="0" t="s">
         <v>217</v>
       </c>
-      <c r="B367" s="0">
-        <v>1</v>
+      <c r="B367" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C367" s="0" t="s">
-        <v>1</v>
+        <v>359</v>
       </c>
       <c r="D367" s="0" t="s">
         <v>237</v>
@@ -7018,11 +7519,11 @@
       <c r="A368" s="0" t="s">
         <v>217</v>
       </c>
-      <c r="B368" s="0">
-        <v>1</v>
+      <c r="B368" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C368" s="0" t="s">
-        <v>1</v>
+        <v>359</v>
       </c>
       <c r="D368" s="0" t="s">
         <v>237</v>
@@ -7035,11 +7536,11 @@
       <c r="A369" s="0" t="s">
         <v>217</v>
       </c>
-      <c r="B369" s="0">
-        <v>1</v>
+      <c r="B369" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C369" s="0" t="s">
-        <v>1</v>
+        <v>359</v>
       </c>
       <c r="D369" s="0" t="s">
         <v>237</v>
@@ -7052,11 +7553,11 @@
       <c r="A370" s="0" t="s">
         <v>217</v>
       </c>
-      <c r="B370" s="0">
-        <v>1</v>
+      <c r="B370" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C370" s="0" t="s">
-        <v>1</v>
+        <v>359</v>
       </c>
       <c r="D370" s="0" t="s">
         <v>237</v>
@@ -7069,11 +7570,11 @@
       <c r="A371" s="0" t="s">
         <v>217</v>
       </c>
-      <c r="B371" s="0">
-        <v>1</v>
+      <c r="B371" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C371" s="0" t="s">
-        <v>1</v>
+        <v>359</v>
       </c>
       <c r="D371" s="0" t="s">
         <v>237</v>
@@ -7086,11 +7587,11 @@
       <c r="A372" s="0" t="s">
         <v>217</v>
       </c>
-      <c r="B372" s="0">
-        <v>2</v>
+      <c r="B372" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C372" s="0" t="s">
-        <v>1</v>
+        <v>360</v>
       </c>
       <c r="D372" s="0" t="s">
         <v>237</v>
@@ -7103,11 +7604,11 @@
       <c r="A373" s="0" t="s">
         <v>217</v>
       </c>
-      <c r="B373" s="0">
-        <v>2</v>
+      <c r="B373" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C373" s="0" t="s">
-        <v>1</v>
+        <v>360</v>
       </c>
       <c r="D373" s="0" t="s">
         <v>237</v>
@@ -7120,11 +7621,11 @@
       <c r="A374" s="0" t="s">
         <v>217</v>
       </c>
-      <c r="B374" s="0">
-        <v>2</v>
+      <c r="B374" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C374" s="0" t="s">
-        <v>1</v>
+        <v>360</v>
       </c>
       <c r="D374" s="0" t="s">
         <v>237</v>
@@ -7137,11 +7638,11 @@
       <c r="A375" s="0" t="s">
         <v>217</v>
       </c>
-      <c r="B375" s="0">
-        <v>2</v>
+      <c r="B375" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C375" s="0" t="s">
-        <v>1</v>
+        <v>360</v>
       </c>
       <c r="D375" s="0" t="s">
         <v>237</v>
@@ -7154,11 +7655,11 @@
       <c r="A376" s="0" t="s">
         <v>217</v>
       </c>
-      <c r="B376" s="0">
-        <v>2</v>
+      <c r="B376" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C376" s="0" t="s">
-        <v>1</v>
+        <v>360</v>
       </c>
       <c r="D376" s="0" t="s">
         <v>237</v>
@@ -7171,11 +7672,11 @@
       <c r="A377" s="0" t="s">
         <v>217</v>
       </c>
-      <c r="B377" s="0">
-        <v>2</v>
+      <c r="B377" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C377" s="0" t="s">
-        <v>1</v>
+        <v>360</v>
       </c>
       <c r="D377" s="0" t="s">
         <v>237</v>
@@ -7188,11 +7689,11 @@
       <c r="A378" s="0" t="s">
         <v>217</v>
       </c>
-      <c r="B378" s="0">
-        <v>2</v>
+      <c r="B378" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C378" s="0" t="s">
-        <v>1</v>
+        <v>360</v>
       </c>
       <c r="D378" s="0" t="s">
         <v>237</v>
@@ -7205,11 +7706,11 @@
       <c r="A379" s="0" t="s">
         <v>217</v>
       </c>
-      <c r="B379" s="0">
-        <v>3</v>
+      <c r="B379" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C379" s="0" t="s">
-        <v>1</v>
+        <v>361</v>
       </c>
       <c r="D379" s="0" t="s">
         <v>237</v>
@@ -7222,11 +7723,11 @@
       <c r="A380" s="0" t="s">
         <v>217</v>
       </c>
-      <c r="B380" s="0">
-        <v>3</v>
+      <c r="B380" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C380" s="0" t="s">
-        <v>1</v>
+        <v>361</v>
       </c>
       <c r="D380" s="0" t="s">
         <v>237</v>
@@ -7239,11 +7740,11 @@
       <c r="A381" s="0" t="s">
         <v>217</v>
       </c>
-      <c r="B381" s="0">
-        <v>3</v>
+      <c r="B381" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C381" s="0" t="s">
-        <v>1</v>
+        <v>361</v>
       </c>
       <c r="D381" s="0" t="s">
         <v>237</v>
@@ -7256,11 +7757,11 @@
       <c r="A382" s="0" t="s">
         <v>217</v>
       </c>
-      <c r="B382" s="0">
-        <v>3</v>
+      <c r="B382" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C382" s="0" t="s">
-        <v>1</v>
+        <v>361</v>
       </c>
       <c r="D382" s="0" t="s">
         <v>237</v>
@@ -7273,11 +7774,11 @@
       <c r="A383" s="0" t="s">
         <v>217</v>
       </c>
-      <c r="B383" s="0">
-        <v>3</v>
+      <c r="B383" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C383" s="0" t="s">
-        <v>1</v>
+        <v>361</v>
       </c>
       <c r="D383" s="0" t="s">
         <v>237</v>
@@ -7290,11 +7791,11 @@
       <c r="A384" s="0" t="s">
         <v>217</v>
       </c>
-      <c r="B384" s="0">
-        <v>3</v>
+      <c r="B384" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C384" s="0" t="s">
-        <v>1</v>
+        <v>361</v>
       </c>
       <c r="D384" s="0" t="s">
         <v>237</v>
@@ -7307,11 +7808,11 @@
       <c r="A385" s="0" t="s">
         <v>217</v>
       </c>
-      <c r="B385" s="0">
-        <v>3</v>
+      <c r="B385" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C385" s="0" t="s">
-        <v>1</v>
+        <v>361</v>
       </c>
       <c r="D385" s="0" t="s">
         <v>237</v>
@@ -7324,11 +7825,11 @@
       <c r="A386" s="0" t="s">
         <v>217</v>
       </c>
-      <c r="B386" s="0">
-        <v>4</v>
+      <c r="B386" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C386" s="0" t="s">
-        <v>1</v>
+        <v>362</v>
       </c>
       <c r="D386" s="0" t="s">
         <v>237</v>
@@ -7341,11 +7842,11 @@
       <c r="A387" s="0" t="s">
         <v>218</v>
       </c>
-      <c r="B387" s="0">
-        <v>1</v>
+      <c r="B387" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C387" s="0" t="s">
-        <v>1</v>
+        <v>363</v>
       </c>
       <c r="D387" s="0" t="s">
         <v>237</v>
@@ -7358,11 +7859,11 @@
       <c r="A388" s="0" t="s">
         <v>218</v>
       </c>
-      <c r="B388" s="0">
-        <v>1</v>
+      <c r="B388" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C388" s="0" t="s">
-        <v>1</v>
+        <v>363</v>
       </c>
       <c r="D388" s="0" t="s">
         <v>237</v>
@@ -7375,11 +7876,11 @@
       <c r="A389" s="0" t="s">
         <v>218</v>
       </c>
-      <c r="B389" s="0">
-        <v>1</v>
+      <c r="B389" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C389" s="0" t="s">
-        <v>1</v>
+        <v>363</v>
       </c>
       <c r="D389" s="0" t="s">
         <v>237</v>
@@ -7392,11 +7893,11 @@
       <c r="A390" s="0" t="s">
         <v>218</v>
       </c>
-      <c r="B390" s="0">
-        <v>1</v>
+      <c r="B390" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C390" s="0" t="s">
-        <v>1</v>
+        <v>363</v>
       </c>
       <c r="D390" s="0" t="s">
         <v>237</v>
@@ -7409,11 +7910,11 @@
       <c r="A391" s="0" t="s">
         <v>218</v>
       </c>
-      <c r="B391" s="0">
-        <v>3</v>
+      <c r="B391" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C391" s="0" t="s">
-        <v>1</v>
+        <v>364</v>
       </c>
       <c r="D391" s="0" t="s">
         <v>237</v>
@@ -7426,11 +7927,11 @@
       <c r="A392" s="0" t="s">
         <v>218</v>
       </c>
-      <c r="B392" s="0">
-        <v>3</v>
+      <c r="B392" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C392" s="0" t="s">
-        <v>1</v>
+        <v>364</v>
       </c>
       <c r="D392" s="0" t="s">
         <v>237</v>
@@ -7443,11 +7944,11 @@
       <c r="A393" s="0" t="s">
         <v>218</v>
       </c>
-      <c r="B393" s="0">
-        <v>4</v>
+      <c r="B393" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C393" s="0" t="s">
-        <v>1</v>
+        <v>365</v>
       </c>
       <c r="D393" s="0" t="s">
         <v>237</v>
@@ -7460,11 +7961,11 @@
       <c r="A394" s="0" t="s">
         <v>219</v>
       </c>
-      <c r="B394" s="0">
-        <v>3</v>
+      <c r="B394" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C394" s="0" t="s">
-        <v>1</v>
+        <v>366</v>
       </c>
       <c r="D394" s="0" t="s">
         <v>237</v>
@@ -7477,11 +7978,11 @@
       <c r="A395" s="0" t="s">
         <v>219</v>
       </c>
-      <c r="B395" s="0">
-        <v>4</v>
+      <c r="B395" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C395" s="0" t="s">
-        <v>1</v>
+        <v>367</v>
       </c>
       <c r="D395" s="0" t="s">
         <v>237</v>
@@ -7494,11 +7995,11 @@
       <c r="A396" s="0" t="s">
         <v>219</v>
       </c>
-      <c r="B396" s="0">
-        <v>4</v>
+      <c r="B396" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C396" s="0" t="s">
-        <v>1</v>
+        <v>367</v>
       </c>
       <c r="D396" s="0" t="s">
         <v>237</v>
@@ -7511,11 +8012,11 @@
       <c r="A397" s="0" t="s">
         <v>220</v>
       </c>
-      <c r="B397" s="0">
-        <v>2</v>
+      <c r="B397" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C397" s="0" t="s">
-        <v>1</v>
+        <v>368</v>
       </c>
       <c r="D397" s="0" t="s">
         <v>237</v>
@@ -7528,11 +8029,11 @@
       <c r="A398" s="0" t="s">
         <v>220</v>
       </c>
-      <c r="B398" s="0">
-        <v>2</v>
+      <c r="B398" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C398" s="0" t="s">
-        <v>1</v>
+        <v>368</v>
       </c>
       <c r="D398" s="0" t="s">
         <v>237</v>
@@ -7545,11 +8046,11 @@
       <c r="A399" s="0" t="s">
         <v>220</v>
       </c>
-      <c r="B399" s="0">
-        <v>2</v>
+      <c r="B399" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C399" s="0" t="s">
-        <v>1</v>
+        <v>368</v>
       </c>
       <c r="D399" s="0" t="s">
         <v>237</v>
@@ -7562,11 +8063,11 @@
       <c r="A400" s="0" t="s">
         <v>221</v>
       </c>
-      <c r="B400" s="0">
-        <v>1</v>
+      <c r="B400" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C400" s="0" t="s">
-        <v>1</v>
+        <v>369</v>
       </c>
       <c r="D400" s="0" t="s">
         <v>237</v>
@@ -7579,11 +8080,11 @@
       <c r="A401" s="0" t="s">
         <v>221</v>
       </c>
-      <c r="B401" s="0">
-        <v>1</v>
+      <c r="B401" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C401" s="0" t="s">
-        <v>1</v>
+        <v>369</v>
       </c>
       <c r="D401" s="0" t="s">
         <v>237</v>
@@ -7596,11 +8097,11 @@
       <c r="A402" s="0" t="s">
         <v>221</v>
       </c>
-      <c r="B402" s="0">
-        <v>1</v>
+      <c r="B402" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C402" s="0" t="s">
-        <v>1</v>
+        <v>369</v>
       </c>
       <c r="D402" s="0" t="s">
         <v>237</v>
@@ -7613,11 +8114,11 @@
       <c r="A403" s="0" t="s">
         <v>221</v>
       </c>
-      <c r="B403" s="0">
-        <v>3</v>
+      <c r="B403" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C403" s="0" t="s">
-        <v>1</v>
+        <v>370</v>
       </c>
       <c r="D403" s="0" t="s">
         <v>237</v>
@@ -7630,11 +8131,11 @@
       <c r="A404" s="0" t="s">
         <v>221</v>
       </c>
-      <c r="B404" s="0">
-        <v>3</v>
+      <c r="B404" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C404" s="0" t="s">
-        <v>1</v>
+        <v>370</v>
       </c>
       <c r="D404" s="0" t="s">
         <v>237</v>
@@ -7647,11 +8148,11 @@
       <c r="A405" s="0" t="s">
         <v>221</v>
       </c>
-      <c r="B405" s="0">
-        <v>3</v>
+      <c r="B405" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C405" s="0" t="s">
-        <v>1</v>
+        <v>370</v>
       </c>
       <c r="D405" s="0" t="s">
         <v>237</v>
@@ -7664,11 +8165,11 @@
       <c r="A406" s="0" t="s">
         <v>221</v>
       </c>
-      <c r="B406" s="0">
-        <v>3</v>
+      <c r="B406" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C406" s="0" t="s">
-        <v>1</v>
+        <v>370</v>
       </c>
       <c r="D406" s="0" t="s">
         <v>237</v>
@@ -7681,11 +8182,11 @@
       <c r="A407" s="0" t="s">
         <v>221</v>
       </c>
-      <c r="B407" s="0">
-        <v>3</v>
+      <c r="B407" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C407" s="0" t="s">
-        <v>1</v>
+        <v>370</v>
       </c>
       <c r="D407" s="0" t="s">
         <v>237</v>
@@ -7698,11 +8199,11 @@
       <c r="A408" s="0" t="s">
         <v>221</v>
       </c>
-      <c r="B408" s="0">
-        <v>3</v>
+      <c r="B408" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C408" s="0" t="s">
-        <v>1</v>
+        <v>370</v>
       </c>
       <c r="D408" s="0" t="s">
         <v>237</v>
@@ -7715,11 +8216,11 @@
       <c r="A409" s="0" t="s">
         <v>222</v>
       </c>
-      <c r="B409" s="0">
-        <v>2</v>
+      <c r="B409" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C409" s="0" t="s">
-        <v>1</v>
+        <v>371</v>
       </c>
       <c r="D409" s="0" t="s">
         <v>237</v>
@@ -7732,11 +8233,11 @@
       <c r="A410" s="0" t="s">
         <v>222</v>
       </c>
-      <c r="B410" s="0">
-        <v>3</v>
+      <c r="B410" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C410" s="0" t="s">
-        <v>1</v>
+        <v>372</v>
       </c>
       <c r="D410" s="0" t="s">
         <v>237</v>
@@ -7749,11 +8250,11 @@
       <c r="A411" s="0" t="s">
         <v>223</v>
       </c>
-      <c r="B411" s="0">
-        <v>3</v>
+      <c r="B411" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C411" s="0" t="s">
-        <v>1</v>
+        <v>373</v>
       </c>
       <c r="D411" s="0" t="s">
         <v>237</v>
@@ -7766,11 +8267,11 @@
       <c r="A412" s="0" t="s">
         <v>223</v>
       </c>
-      <c r="B412" s="0">
-        <v>3</v>
+      <c r="B412" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C412" s="0" t="s">
-        <v>1</v>
+        <v>373</v>
       </c>
       <c r="D412" s="0" t="s">
         <v>237</v>
@@ -7783,11 +8284,11 @@
       <c r="A413" s="0" t="s">
         <v>223</v>
       </c>
-      <c r="B413" s="0">
-        <v>3</v>
+      <c r="B413" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C413" s="0" t="s">
-        <v>1</v>
+        <v>373</v>
       </c>
       <c r="D413" s="0" t="s">
         <v>237</v>
@@ -7800,11 +8301,11 @@
       <c r="A414" s="0" t="s">
         <v>223</v>
       </c>
-      <c r="B414" s="0">
-        <v>3</v>
+      <c r="B414" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C414" s="0" t="s">
-        <v>1</v>
+        <v>373</v>
       </c>
       <c r="D414" s="0" t="s">
         <v>237</v>
@@ -7817,11 +8318,11 @@
       <c r="A415" s="0" t="s">
         <v>223</v>
       </c>
-      <c r="B415" s="0">
-        <v>3</v>
+      <c r="B415" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C415" s="0" t="s">
-        <v>1</v>
+        <v>373</v>
       </c>
       <c r="D415" s="0" t="s">
         <v>237</v>
@@ -7834,11 +8335,11 @@
       <c r="A416" s="0" t="s">
         <v>223</v>
       </c>
-      <c r="B416" s="0">
-        <v>3</v>
+      <c r="B416" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C416" s="0" t="s">
-        <v>1</v>
+        <v>373</v>
       </c>
       <c r="D416" s="0" t="s">
         <v>237</v>
@@ -7851,11 +8352,11 @@
       <c r="A417" s="0" t="s">
         <v>223</v>
       </c>
-      <c r="B417" s="0">
-        <v>4</v>
+      <c r="B417" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C417" s="0" t="s">
-        <v>1</v>
+        <v>374</v>
       </c>
       <c r="D417" s="0" t="s">
         <v>237</v>
@@ -7868,11 +8369,11 @@
       <c r="A418" s="0" t="s">
         <v>224</v>
       </c>
-      <c r="B418" s="0">
-        <v>4</v>
+      <c r="B418" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C418" s="0" t="s">
-        <v>1</v>
+        <v>375</v>
       </c>
       <c r="D418" s="0" t="s">
         <v>237</v>
@@ -7885,11 +8386,11 @@
       <c r="A419" s="0" t="s">
         <v>224</v>
       </c>
-      <c r="B419" s="0">
-        <v>4</v>
+      <c r="B419" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C419" s="0" t="s">
-        <v>1</v>
+        <v>375</v>
       </c>
       <c r="D419" s="0" t="s">
         <v>237</v>
@@ -7902,11 +8403,11 @@
       <c r="A420" s="0" t="s">
         <v>225</v>
       </c>
-      <c r="B420" s="0">
-        <v>1</v>
+      <c r="B420" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C420" s="0" t="s">
-        <v>1</v>
+        <v>376</v>
       </c>
       <c r="D420" s="0" t="s">
         <v>237</v>
@@ -7919,11 +8420,11 @@
       <c r="A421" s="0" t="s">
         <v>225</v>
       </c>
-      <c r="B421" s="0">
-        <v>2</v>
+      <c r="B421" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C421" s="0" t="s">
-        <v>1</v>
+        <v>377</v>
       </c>
       <c r="D421" s="0" t="s">
         <v>237</v>
@@ -7936,11 +8437,11 @@
       <c r="A422" s="0" t="s">
         <v>225</v>
       </c>
-      <c r="B422" s="0">
-        <v>2</v>
+      <c r="B422" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C422" s="0" t="s">
-        <v>1</v>
+        <v>377</v>
       </c>
       <c r="D422" s="0" t="s">
         <v>237</v>
@@ -7953,11 +8454,11 @@
       <c r="A423" s="0" t="s">
         <v>225</v>
       </c>
-      <c r="B423" s="0">
-        <v>3</v>
+      <c r="B423" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C423" s="0" t="s">
-        <v>1</v>
+        <v>378</v>
       </c>
       <c r="D423" s="0" t="s">
         <v>237</v>
@@ -7970,11 +8471,11 @@
       <c r="A424" s="0" t="s">
         <v>225</v>
       </c>
-      <c r="B424" s="0">
-        <v>3</v>
+      <c r="B424" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C424" s="0" t="s">
-        <v>1</v>
+        <v>378</v>
       </c>
       <c r="D424" s="0" t="s">
         <v>237</v>
@@ -7987,11 +8488,11 @@
       <c r="A425" s="0" t="s">
         <v>225</v>
       </c>
-      <c r="B425" s="0">
-        <v>3</v>
+      <c r="B425" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C425" s="0" t="s">
-        <v>1</v>
+        <v>378</v>
       </c>
       <c r="D425" s="0" t="s">
         <v>237</v>
@@ -8004,11 +8505,11 @@
       <c r="A426" s="0" t="s">
         <v>225</v>
       </c>
-      <c r="B426" s="0">
-        <v>3</v>
+      <c r="B426" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C426" s="0" t="s">
-        <v>1</v>
+        <v>378</v>
       </c>
       <c r="D426" s="0" t="s">
         <v>237</v>
@@ -8021,11 +8522,11 @@
       <c r="A427" s="0" t="s">
         <v>225</v>
       </c>
-      <c r="B427" s="0">
-        <v>3</v>
+      <c r="B427" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C427" s="0" t="s">
-        <v>1</v>
+        <v>378</v>
       </c>
       <c r="D427" s="0" t="s">
         <v>237</v>
@@ -8038,11 +8539,11 @@
       <c r="A428" s="0" t="s">
         <v>226</v>
       </c>
-      <c r="B428" s="0">
-        <v>1</v>
+      <c r="B428" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C428" s="0" t="s">
-        <v>1</v>
+        <v>379</v>
       </c>
       <c r="D428" s="0" t="s">
         <v>237</v>
@@ -8055,11 +8556,11 @@
       <c r="A429" s="0" t="s">
         <v>226</v>
       </c>
-      <c r="B429" s="0">
-        <v>2</v>
+      <c r="B429" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C429" s="0" t="s">
-        <v>1</v>
+        <v>380</v>
       </c>
       <c r="D429" s="0" t="s">
         <v>237</v>
@@ -8072,11 +8573,11 @@
       <c r="A430" s="0" t="s">
         <v>226</v>
       </c>
-      <c r="B430" s="0">
-        <v>2</v>
+      <c r="B430" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C430" s="0" t="s">
-        <v>1</v>
+        <v>380</v>
       </c>
       <c r="D430" s="0" t="s">
         <v>237</v>
@@ -8089,11 +8590,11 @@
       <c r="A431" s="0" t="s">
         <v>227</v>
       </c>
-      <c r="B431" s="0">
-        <v>1</v>
+      <c r="B431" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C431" s="0" t="s">
-        <v>1</v>
+        <v>381</v>
       </c>
       <c r="D431" s="0" t="s">
         <v>237</v>
@@ -8106,11 +8607,11 @@
       <c r="A432" s="0" t="s">
         <v>227</v>
       </c>
-      <c r="B432" s="0">
-        <v>2</v>
+      <c r="B432" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C432" s="0" t="s">
-        <v>1</v>
+        <v>382</v>
       </c>
       <c r="D432" s="0" t="s">
         <v>237</v>
@@ -8123,11 +8624,11 @@
       <c r="A433" s="0" t="s">
         <v>227</v>
       </c>
-      <c r="B433" s="0">
-        <v>2</v>
+      <c r="B433" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C433" s="0" t="s">
-        <v>1</v>
+        <v>382</v>
       </c>
       <c r="D433" s="0" t="s">
         <v>237</v>
@@ -8140,11 +8641,11 @@
       <c r="A434" s="0" t="s">
         <v>227</v>
       </c>
-      <c r="B434" s="0">
-        <v>2</v>
+      <c r="B434" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C434" s="0" t="s">
-        <v>1</v>
+        <v>382</v>
       </c>
       <c r="D434" s="0" t="s">
         <v>237</v>
@@ -8157,11 +8658,11 @@
       <c r="A435" s="0" t="s">
         <v>227</v>
       </c>
-      <c r="B435" s="0">
-        <v>3</v>
+      <c r="B435" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C435" s="0" t="s">
-        <v>1</v>
+        <v>383</v>
       </c>
       <c r="D435" s="0" t="s">
         <v>237</v>
@@ -8174,11 +8675,11 @@
       <c r="A436" s="0" t="s">
         <v>227</v>
       </c>
-      <c r="B436" s="0">
-        <v>4</v>
+      <c r="B436" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C436" s="0" t="s">
-        <v>1</v>
+        <v>384</v>
       </c>
       <c r="D436" s="0" t="s">
         <v>237</v>
@@ -8191,11 +8692,11 @@
       <c r="A437" s="0" t="s">
         <v>227</v>
       </c>
-      <c r="B437" s="0">
-        <v>4</v>
+      <c r="B437" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C437" s="0" t="s">
-        <v>1</v>
+        <v>384</v>
       </c>
       <c r="D437" s="0" t="s">
         <v>237</v>
@@ -8208,11 +8709,11 @@
       <c r="A438" s="0" t="s">
         <v>228</v>
       </c>
-      <c r="B438" s="0">
-        <v>1</v>
+      <c r="B438" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C438" s="0" t="s">
-        <v>1</v>
+        <v>385</v>
       </c>
       <c r="D438" s="0" t="s">
         <v>237</v>
@@ -8225,11 +8726,11 @@
       <c r="A439" s="0" t="s">
         <v>228</v>
       </c>
-      <c r="B439" s="0">
-        <v>1</v>
+      <c r="B439" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C439" s="0" t="s">
-        <v>1</v>
+        <v>385</v>
       </c>
       <c r="D439" s="0" t="s">
         <v>237</v>
@@ -8242,11 +8743,11 @@
       <c r="A440" s="0" t="s">
         <v>228</v>
       </c>
-      <c r="B440" s="0">
-        <v>2</v>
+      <c r="B440" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C440" s="0" t="s">
-        <v>1</v>
+        <v>386</v>
       </c>
       <c r="D440" s="0" t="s">
         <v>237</v>
@@ -8259,11 +8760,11 @@
       <c r="A441" s="0" t="s">
         <v>228</v>
       </c>
-      <c r="B441" s="0">
-        <v>2</v>
+      <c r="B441" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C441" s="0" t="s">
-        <v>1</v>
+        <v>386</v>
       </c>
       <c r="D441" s="0" t="s">
         <v>237</v>
@@ -8276,11 +8777,11 @@
       <c r="A442" s="0" t="s">
         <v>228</v>
       </c>
-      <c r="B442" s="0">
-        <v>2</v>
+      <c r="B442" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C442" s="0" t="s">
-        <v>1</v>
+        <v>386</v>
       </c>
       <c r="D442" s="0" t="s">
         <v>237</v>
@@ -8293,11 +8794,11 @@
       <c r="A443" s="0" t="s">
         <v>228</v>
       </c>
-      <c r="B443" s="0">
-        <v>2</v>
+      <c r="B443" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C443" s="0" t="s">
-        <v>1</v>
+        <v>386</v>
       </c>
       <c r="D443" s="0" t="s">
         <v>237</v>
@@ -8310,11 +8811,11 @@
       <c r="A444" s="0" t="s">
         <v>228</v>
       </c>
-      <c r="B444" s="0">
-        <v>3</v>
+      <c r="B444" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C444" s="0" t="s">
-        <v>1</v>
+        <v>387</v>
       </c>
       <c r="D444" s="0" t="s">
         <v>237</v>
@@ -8327,11 +8828,11 @@
       <c r="A445" s="0" t="s">
         <v>228</v>
       </c>
-      <c r="B445" s="0">
-        <v>3</v>
+      <c r="B445" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C445" s="0" t="s">
-        <v>1</v>
+        <v>387</v>
       </c>
       <c r="D445" s="0" t="s">
         <v>237</v>
@@ -8344,11 +8845,11 @@
       <c r="A446" s="0" t="s">
         <v>228</v>
       </c>
-      <c r="B446" s="0">
-        <v>3</v>
+      <c r="B446" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C446" s="0" t="s">
-        <v>1</v>
+        <v>387</v>
       </c>
       <c r="D446" s="0" t="s">
         <v>237</v>
@@ -8361,11 +8862,11 @@
       <c r="A447" s="0" t="s">
         <v>228</v>
       </c>
-      <c r="B447" s="0">
-        <v>3</v>
+      <c r="B447" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C447" s="0" t="s">
-        <v>1</v>
+        <v>387</v>
       </c>
       <c r="D447" s="0" t="s">
         <v>237</v>
@@ -8378,11 +8879,11 @@
       <c r="A448" s="0" t="s">
         <v>228</v>
       </c>
-      <c r="B448" s="0">
-        <v>3</v>
+      <c r="B448" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C448" s="0" t="s">
-        <v>1</v>
+        <v>387</v>
       </c>
       <c r="D448" s="0" t="s">
         <v>237</v>
@@ -8395,11 +8896,11 @@
       <c r="A449" s="0" t="s">
         <v>228</v>
       </c>
-      <c r="B449" s="0">
-        <v>4</v>
+      <c r="B449" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C449" s="0" t="s">
-        <v>1</v>
+        <v>388</v>
       </c>
       <c r="D449" s="0" t="s">
         <v>237</v>
@@ -8412,11 +8913,11 @@
       <c r="A450" s="0" t="s">
         <v>228</v>
       </c>
-      <c r="B450" s="0">
-        <v>4</v>
+      <c r="B450" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C450" s="0" t="s">
-        <v>1</v>
+        <v>388</v>
       </c>
       <c r="D450" s="0" t="s">
         <v>237</v>
@@ -8429,11 +8930,11 @@
       <c r="A451" s="0" t="s">
         <v>228</v>
       </c>
-      <c r="B451" s="0">
-        <v>4</v>
+      <c r="B451" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C451" s="0" t="s">
-        <v>1</v>
+        <v>388</v>
       </c>
       <c r="D451" s="0" t="s">
         <v>237</v>
@@ -8446,11 +8947,11 @@
       <c r="A452" s="0" t="s">
         <v>228</v>
       </c>
-      <c r="B452" s="0">
-        <v>4</v>
+      <c r="B452" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C452" s="0" t="s">
-        <v>1</v>
+        <v>388</v>
       </c>
       <c r="D452" s="0" t="s">
         <v>237</v>
@@ -8463,11 +8964,11 @@
       <c r="A453" s="0" t="s">
         <v>229</v>
       </c>
-      <c r="B453" s="0">
-        <v>1</v>
+      <c r="B453" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C453" s="0" t="s">
-        <v>1</v>
+        <v>389</v>
       </c>
       <c r="D453" s="0" t="s">
         <v>237</v>
@@ -8480,11 +8981,11 @@
       <c r="A454" s="0" t="s">
         <v>229</v>
       </c>
-      <c r="B454" s="0">
-        <v>4</v>
+      <c r="B454" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C454" s="0" t="s">
-        <v>1</v>
+        <v>390</v>
       </c>
       <c r="D454" s="0" t="s">
         <v>237</v>
@@ -8497,11 +8998,11 @@
       <c r="A455" s="0" t="s">
         <v>229</v>
       </c>
-      <c r="B455" s="0">
-        <v>4</v>
+      <c r="B455" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C455" s="0" t="s">
-        <v>1</v>
+        <v>390</v>
       </c>
       <c r="D455" s="0" t="s">
         <v>237</v>
@@ -8514,11 +9015,11 @@
       <c r="A456" s="0" t="s">
         <v>230</v>
       </c>
-      <c r="B456" s="0">
-        <v>2</v>
+      <c r="B456" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C456" s="0" t="s">
-        <v>1</v>
+        <v>391</v>
       </c>
       <c r="D456" s="0" t="s">
         <v>237</v>
@@ -8531,11 +9032,11 @@
       <c r="A457" s="0" t="s">
         <v>230</v>
       </c>
-      <c r="B457" s="0">
-        <v>2</v>
+      <c r="B457" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C457" s="0" t="s">
-        <v>1</v>
+        <v>391</v>
       </c>
       <c r="D457" s="0" t="s">
         <v>237</v>
@@ -8548,11 +9049,11 @@
       <c r="A458" s="0" t="s">
         <v>230</v>
       </c>
-      <c r="B458" s="0">
-        <v>3</v>
+      <c r="B458" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C458" s="0" t="s">
-        <v>1</v>
+        <v>392</v>
       </c>
       <c r="D458" s="0" t="s">
         <v>237</v>
@@ -8565,11 +9066,11 @@
       <c r="A459" s="0" t="s">
         <v>230</v>
       </c>
-      <c r="B459" s="0">
-        <v>3</v>
+      <c r="B459" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C459" s="0" t="s">
-        <v>1</v>
+        <v>392</v>
       </c>
       <c r="D459" s="0" t="s">
         <v>237</v>
@@ -8582,11 +9083,11 @@
       <c r="A460" s="0" t="s">
         <v>230</v>
       </c>
-      <c r="B460" s="0">
-        <v>3</v>
+      <c r="B460" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C460" s="0" t="s">
-        <v>1</v>
+        <v>392</v>
       </c>
       <c r="D460" s="0" t="s">
         <v>237</v>
@@ -8599,11 +9100,11 @@
       <c r="A461" s="0" t="s">
         <v>230</v>
       </c>
-      <c r="B461" s="0">
-        <v>3</v>
+      <c r="B461" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C461" s="0" t="s">
-        <v>1</v>
+        <v>392</v>
       </c>
       <c r="D461" s="0" t="s">
         <v>237</v>
@@ -8616,11 +9117,11 @@
       <c r="A462" s="0" t="s">
         <v>230</v>
       </c>
-      <c r="B462" s="0">
-        <v>3</v>
+      <c r="B462" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C462" s="0" t="s">
-        <v>1</v>
+        <v>392</v>
       </c>
       <c r="D462" s="0" t="s">
         <v>237</v>
@@ -8633,11 +9134,11 @@
       <c r="A463" s="0" t="s">
         <v>231</v>
       </c>
-      <c r="B463" s="0">
-        <v>2</v>
+      <c r="B463" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C463" s="0" t="s">
-        <v>1</v>
+        <v>393</v>
       </c>
       <c r="D463" s="0" t="s">
         <v>237</v>
@@ -8650,11 +9151,11 @@
       <c r="A464" s="0" t="s">
         <v>231</v>
       </c>
-      <c r="B464" s="0">
-        <v>3</v>
+      <c r="B464" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C464" s="0" t="s">
-        <v>1</v>
+        <v>394</v>
       </c>
       <c r="D464" s="0" t="s">
         <v>237</v>
@@ -8667,11 +9168,11 @@
       <c r="A465" s="0" t="s">
         <v>231</v>
       </c>
-      <c r="B465" s="0">
-        <v>3</v>
+      <c r="B465" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C465" s="0" t="s">
-        <v>1</v>
+        <v>394</v>
       </c>
       <c r="D465" s="0" t="s">
         <v>237</v>
@@ -8684,11 +9185,11 @@
       <c r="A466" s="0" t="s">
         <v>231</v>
       </c>
-      <c r="B466" s="0">
-        <v>3</v>
+      <c r="B466" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C466" s="0" t="s">
-        <v>1</v>
+        <v>394</v>
       </c>
       <c r="D466" s="0" t="s">
         <v>237</v>
@@ -8701,11 +9202,11 @@
       <c r="A467" s="0" t="s">
         <v>231</v>
       </c>
-      <c r="B467" s="0">
-        <v>3</v>
+      <c r="B467" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C467" s="0" t="s">
-        <v>1</v>
+        <v>394</v>
       </c>
       <c r="D467" s="0" t="s">
         <v>237</v>
@@ -8718,11 +9219,11 @@
       <c r="A468" s="0" t="s">
         <v>231</v>
       </c>
-      <c r="B468" s="0">
-        <v>3</v>
+      <c r="B468" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C468" s="0" t="s">
-        <v>1</v>
+        <v>394</v>
       </c>
       <c r="D468" s="0" t="s">
         <v>237</v>
@@ -8735,11 +9236,11 @@
       <c r="A469" s="0" t="s">
         <v>231</v>
       </c>
-      <c r="B469" s="0">
-        <v>3</v>
+      <c r="B469" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C469" s="0" t="s">
-        <v>1</v>
+        <v>394</v>
       </c>
       <c r="D469" s="0" t="s">
         <v>237</v>
@@ -8752,11 +9253,11 @@
       <c r="A470" s="0" t="s">
         <v>231</v>
       </c>
-      <c r="B470" s="0">
-        <v>4</v>
+      <c r="B470" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C470" s="0" t="s">
-        <v>1</v>
+        <v>395</v>
       </c>
       <c r="D470" s="0" t="s">
         <v>237</v>
@@ -8769,11 +9270,11 @@
       <c r="A471" s="0" t="s">
         <v>232</v>
       </c>
-      <c r="B471" s="0">
-        <v>2</v>
+      <c r="B471" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C471" s="0" t="s">
-        <v>1</v>
+        <v>396</v>
       </c>
       <c r="D471" s="0" t="s">
         <v>237</v>
@@ -8786,11 +9287,11 @@
       <c r="A472" s="0" t="s">
         <v>232</v>
       </c>
-      <c r="B472" s="0">
-        <v>2</v>
+      <c r="B472" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C472" s="0" t="s">
-        <v>1</v>
+        <v>396</v>
       </c>
       <c r="D472" s="0" t="s">
         <v>237</v>
@@ -8803,11 +9304,11 @@
       <c r="A473" s="0" t="s">
         <v>232</v>
       </c>
-      <c r="B473" s="0">
-        <v>2</v>
+      <c r="B473" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C473" s="0" t="s">
-        <v>1</v>
+        <v>396</v>
       </c>
       <c r="D473" s="0" t="s">
         <v>237</v>
@@ -8820,11 +9321,11 @@
       <c r="A474" s="0" t="s">
         <v>232</v>
       </c>
-      <c r="B474" s="0">
-        <v>2</v>
+      <c r="B474" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C474" s="0" t="s">
-        <v>1</v>
+        <v>396</v>
       </c>
       <c r="D474" s="0" t="s">
         <v>237</v>
@@ -8837,11 +9338,11 @@
       <c r="A475" s="0" t="s">
         <v>232</v>
       </c>
-      <c r="B475" s="0">
-        <v>3</v>
+      <c r="B475" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C475" s="0" t="s">
-        <v>1</v>
+        <v>397</v>
       </c>
       <c r="D475" s="0" t="s">
         <v>237</v>
@@ -8854,11 +9355,11 @@
       <c r="A476" s="0" t="s">
         <v>232</v>
       </c>
-      <c r="B476" s="0">
-        <v>3</v>
+      <c r="B476" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C476" s="0" t="s">
-        <v>1</v>
+        <v>397</v>
       </c>
       <c r="D476" s="0" t="s">
         <v>237</v>
@@ -8871,11 +9372,11 @@
       <c r="A477" s="0" t="s">
         <v>232</v>
       </c>
-      <c r="B477" s="0">
-        <v>3</v>
+      <c r="B477" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C477" s="0" t="s">
-        <v>1</v>
+        <v>397</v>
       </c>
       <c r="D477" s="0" t="s">
         <v>237</v>
@@ -8888,11 +9389,11 @@
       <c r="A478" s="0" t="s">
         <v>232</v>
       </c>
-      <c r="B478" s="0">
-        <v>3</v>
+      <c r="B478" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C478" s="0" t="s">
-        <v>1</v>
+        <v>397</v>
       </c>
       <c r="D478" s="0" t="s">
         <v>237</v>
@@ -8905,11 +9406,11 @@
       <c r="A479" s="0" t="s">
         <v>232</v>
       </c>
-      <c r="B479" s="0">
-        <v>3</v>
+      <c r="B479" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C479" s="0" t="s">
-        <v>1</v>
+        <v>397</v>
       </c>
       <c r="D479" s="0" t="s">
         <v>237</v>
@@ -8922,11 +9423,11 @@
       <c r="A480" s="0" t="s">
         <v>232</v>
       </c>
-      <c r="B480" s="0">
-        <v>3</v>
+      <c r="B480" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C480" s="0" t="s">
-        <v>1</v>
+        <v>397</v>
       </c>
       <c r="D480" s="0" t="s">
         <v>237</v>
@@ -8939,11 +9440,11 @@
       <c r="A481" s="0" t="s">
         <v>232</v>
       </c>
-      <c r="B481" s="0">
-        <v>4</v>
+      <c r="B481" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C481" s="0" t="s">
-        <v>1</v>
+        <v>398</v>
       </c>
       <c r="D481" s="0" t="s">
         <v>237</v>
@@ -8956,11 +9457,11 @@
       <c r="A482" s="0" t="s">
         <v>232</v>
       </c>
-      <c r="B482" s="0">
-        <v>4</v>
+      <c r="B482" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C482" s="0" t="s">
-        <v>1</v>
+        <v>398</v>
       </c>
       <c r="D482" s="0" t="s">
         <v>237</v>
@@ -8973,11 +9474,11 @@
       <c r="A483" s="0" t="s">
         <v>233</v>
       </c>
-      <c r="B483" s="0">
-        <v>4</v>
+      <c r="B483" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C483" s="0" t="s">
-        <v>1</v>
+        <v>399</v>
       </c>
       <c r="D483" s="0" t="s">
         <v>237</v>
@@ -8990,11 +9491,11 @@
       <c r="A484" s="0" t="s">
         <v>233</v>
       </c>
-      <c r="B484" s="0">
-        <v>4</v>
+      <c r="B484" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C484" s="0" t="s">
-        <v>1</v>
+        <v>399</v>
       </c>
       <c r="D484" s="0" t="s">
         <v>237</v>
@@ -9007,11 +9508,11 @@
       <c r="A485" s="0" t="s">
         <v>233</v>
       </c>
-      <c r="B485" s="0">
-        <v>4</v>
+      <c r="B485" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C485" s="0" t="s">
-        <v>1</v>
+        <v>399</v>
       </c>
       <c r="D485" s="0" t="s">
         <v>237</v>
@@ -9024,11 +9525,11 @@
       <c r="A486" s="0" t="s">
         <v>234</v>
       </c>
-      <c r="B486" s="0">
-        <v>1</v>
+      <c r="B486" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C486" s="0" t="s">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="D486" s="0" t="s">
         <v>237</v>
@@ -9041,11 +9542,11 @@
       <c r="A487" s="0" t="s">
         <v>234</v>
       </c>
-      <c r="B487" s="0">
-        <v>1</v>
+      <c r="B487" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C487" s="0" t="s">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="D487" s="0" t="s">
         <v>237</v>
@@ -9058,11 +9559,11 @@
       <c r="A488" s="0" t="s">
         <v>234</v>
       </c>
-      <c r="B488" s="0">
-        <v>1</v>
+      <c r="B488" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C488" s="0" t="s">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="D488" s="0" t="s">
         <v>237</v>
@@ -9075,11 +9576,11 @@
       <c r="A489" s="0" t="s">
         <v>234</v>
       </c>
-      <c r="B489" s="0">
-        <v>2</v>
+      <c r="B489" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C489" s="0" t="s">
-        <v>1</v>
+        <v>401</v>
       </c>
       <c r="D489" s="0" t="s">
         <v>237</v>
@@ -9092,11 +9593,11 @@
       <c r="A490" s="0" t="s">
         <v>234</v>
       </c>
-      <c r="B490" s="0">
-        <v>2</v>
+      <c r="B490" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C490" s="0" t="s">
-        <v>1</v>
+        <v>401</v>
       </c>
       <c r="D490" s="0" t="s">
         <v>237</v>
@@ -9109,11 +9610,11 @@
       <c r="A491" s="0" t="s">
         <v>234</v>
       </c>
-      <c r="B491" s="0">
-        <v>2</v>
+      <c r="B491" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C491" s="0" t="s">
-        <v>1</v>
+        <v>401</v>
       </c>
       <c r="D491" s="0" t="s">
         <v>237</v>
@@ -9126,11 +9627,11 @@
       <c r="A492" s="0" t="s">
         <v>234</v>
       </c>
-      <c r="B492" s="0">
-        <v>2</v>
+      <c r="B492" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C492" s="0" t="s">
-        <v>1</v>
+        <v>401</v>
       </c>
       <c r="D492" s="0" t="s">
         <v>237</v>
@@ -9143,11 +9644,11 @@
       <c r="A493" s="0" t="s">
         <v>234</v>
       </c>
-      <c r="B493" s="0">
-        <v>3</v>
+      <c r="B493" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C493" s="0" t="s">
-        <v>1</v>
+        <v>402</v>
       </c>
       <c r="D493" s="0" t="s">
         <v>237</v>
@@ -9160,11 +9661,11 @@
       <c r="A494" s="0" t="s">
         <v>234</v>
       </c>
-      <c r="B494" s="0">
-        <v>3</v>
+      <c r="B494" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C494" s="0" t="s">
-        <v>1</v>
+        <v>402</v>
       </c>
       <c r="D494" s="0" t="s">
         <v>237</v>
@@ -9177,11 +9678,11 @@
       <c r="A495" s="0" t="s">
         <v>234</v>
       </c>
-      <c r="B495" s="0">
-        <v>4</v>
+      <c r="B495" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C495" s="0" t="s">
-        <v>1</v>
+        <v>403</v>
       </c>
       <c r="D495" s="0" t="s">
         <v>237</v>
@@ -9194,11 +9695,11 @@
       <c r="A496" s="0" t="s">
         <v>234</v>
       </c>
-      <c r="B496" s="0">
-        <v>4</v>
+      <c r="B496" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C496" s="0" t="s">
-        <v>1</v>
+        <v>403</v>
       </c>
       <c r="D496" s="0" t="s">
         <v>237</v>
@@ -9211,11 +9712,11 @@
       <c r="A497" s="0" t="s">
         <v>234</v>
       </c>
-      <c r="B497" s="0">
-        <v>4</v>
+      <c r="B497" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C497" s="0" t="s">
-        <v>1</v>
+        <v>403</v>
       </c>
       <c r="D497" s="0" t="s">
         <v>237</v>
@@ -9228,11 +9729,11 @@
       <c r="A498" s="0" t="s">
         <v>234</v>
       </c>
-      <c r="B498" s="0">
-        <v>4</v>
+      <c r="B498" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C498" s="0" t="s">
-        <v>1</v>
+        <v>403</v>
       </c>
       <c r="D498" s="0" t="s">
         <v>237</v>
@@ -9245,11 +9746,11 @@
       <c r="A499" s="0" t="s">
         <v>234</v>
       </c>
-      <c r="B499" s="0">
-        <v>4</v>
+      <c r="B499" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C499" s="0" t="s">
-        <v>1</v>
+        <v>403</v>
       </c>
       <c r="D499" s="0" t="s">
         <v>237</v>
@@ -9262,11 +9763,11 @@
       <c r="A500" s="0" t="s">
         <v>234</v>
       </c>
-      <c r="B500" s="0">
-        <v>4</v>
+      <c r="B500" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C500" s="0" t="s">
-        <v>1</v>
+        <v>403</v>
       </c>
       <c r="D500" s="0" t="s">
         <v>237</v>
@@ -9279,11 +9780,11 @@
       <c r="A501" s="0" t="s">
         <v>234</v>
       </c>
-      <c r="B501" s="0">
-        <v>4</v>
+      <c r="B501" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C501" s="0" t="s">
-        <v>1</v>
+        <v>403</v>
       </c>
       <c r="D501" s="0" t="s">
         <v>237</v>
@@ -9296,11 +9797,11 @@
       <c r="A502" s="0" t="s">
         <v>234</v>
       </c>
-      <c r="B502" s="0">
-        <v>4</v>
+      <c r="B502" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C502" s="0" t="s">
-        <v>1</v>
+        <v>403</v>
       </c>
       <c r="D502" s="0" t="s">
         <v>237</v>
@@ -9313,11 +9814,11 @@
       <c r="A503" s="0" t="s">
         <v>235</v>
       </c>
-      <c r="B503" s="0">
-        <v>1</v>
+      <c r="B503" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C503" s="0" t="s">
-        <v>1</v>
+        <v>404</v>
       </c>
       <c r="D503" s="0" t="s">
         <v>237</v>
@@ -9330,11 +9831,11 @@
       <c r="A504" s="0" t="s">
         <v>235</v>
       </c>
-      <c r="B504" s="0">
-        <v>1</v>
+      <c r="B504" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C504" s="0" t="s">
-        <v>1</v>
+        <v>404</v>
       </c>
       <c r="D504" s="0" t="s">
         <v>237</v>
@@ -9347,11 +9848,11 @@
       <c r="A505" s="0" t="s">
         <v>235</v>
       </c>
-      <c r="B505" s="0">
-        <v>1</v>
+      <c r="B505" s="0" t="s">
+        <v>179</v>
       </c>
       <c r="C505" s="0" t="s">
-        <v>1</v>
+        <v>404</v>
       </c>
       <c r="D505" s="0" t="s">
         <v>237</v>
@@ -9364,11 +9865,11 @@
       <c r="A506" s="0" t="s">
         <v>235</v>
       </c>
-      <c r="B506" s="0">
-        <v>2</v>
+      <c r="B506" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C506" s="0" t="s">
-        <v>1</v>
+        <v>405</v>
       </c>
       <c r="D506" s="0" t="s">
         <v>237</v>
@@ -9381,11 +9882,11 @@
       <c r="A507" s="0" t="s">
         <v>235</v>
       </c>
-      <c r="B507" s="0">
-        <v>2</v>
+      <c r="B507" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C507" s="0" t="s">
-        <v>1</v>
+        <v>405</v>
       </c>
       <c r="D507" s="0" t="s">
         <v>237</v>
@@ -9398,11 +9899,11 @@
       <c r="A508" s="0" t="s">
         <v>235</v>
       </c>
-      <c r="B508" s="0">
-        <v>2</v>
+      <c r="B508" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C508" s="0" t="s">
-        <v>1</v>
+        <v>405</v>
       </c>
       <c r="D508" s="0" t="s">
         <v>237</v>
@@ -9415,11 +9916,11 @@
       <c r="A509" s="0" t="s">
         <v>235</v>
       </c>
-      <c r="B509" s="0">
-        <v>2</v>
+      <c r="B509" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C509" s="0" t="s">
-        <v>1</v>
+        <v>405</v>
       </c>
       <c r="D509" s="0" t="s">
         <v>237</v>
@@ -9432,11 +9933,11 @@
       <c r="A510" s="0" t="s">
         <v>235</v>
       </c>
-      <c r="B510" s="0">
-        <v>2</v>
+      <c r="B510" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C510" s="0" t="s">
-        <v>1</v>
+        <v>405</v>
       </c>
       <c r="D510" s="0" t="s">
         <v>237</v>
@@ -9449,11 +9950,11 @@
       <c r="A511" s="0" t="s">
         <v>235</v>
       </c>
-      <c r="B511" s="0">
-        <v>2</v>
+      <c r="B511" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C511" s="0" t="s">
-        <v>1</v>
+        <v>405</v>
       </c>
       <c r="D511" s="0" t="s">
         <v>237</v>
@@ -9466,11 +9967,11 @@
       <c r="A512" s="0" t="s">
         <v>235</v>
       </c>
-      <c r="B512" s="0">
-        <v>2</v>
+      <c r="B512" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C512" s="0" t="s">
-        <v>1</v>
+        <v>405</v>
       </c>
       <c r="D512" s="0" t="s">
         <v>237</v>
@@ -9483,11 +9984,11 @@
       <c r="A513" s="0" t="s">
         <v>235</v>
       </c>
-      <c r="B513" s="0">
-        <v>2</v>
+      <c r="B513" s="0" t="s">
+        <v>248</v>
       </c>
       <c r="C513" s="0" t="s">
-        <v>1</v>
+        <v>405</v>
       </c>
       <c r="D513" s="0" t="s">
         <v>237</v>
@@ -9500,11 +10001,11 @@
       <c r="A514" s="0" t="s">
         <v>235</v>
       </c>
-      <c r="B514" s="0">
-        <v>3</v>
+      <c r="B514" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C514" s="0" t="s">
-        <v>1</v>
+        <v>406</v>
       </c>
       <c r="D514" s="0" t="s">
         <v>237</v>
@@ -9517,11 +10018,11 @@
       <c r="A515" s="0" t="s">
         <v>235</v>
       </c>
-      <c r="B515" s="0">
-        <v>3</v>
+      <c r="B515" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C515" s="0" t="s">
-        <v>1</v>
+        <v>406</v>
       </c>
       <c r="D515" s="0" t="s">
         <v>237</v>
@@ -9534,11 +10035,11 @@
       <c r="A516" s="0" t="s">
         <v>235</v>
       </c>
-      <c r="B516" s="0">
-        <v>3</v>
+      <c r="B516" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C516" s="0" t="s">
-        <v>1</v>
+        <v>406</v>
       </c>
       <c r="D516" s="0" t="s">
         <v>237</v>
@@ -9551,11 +10052,11 @@
       <c r="A517" s="0" t="s">
         <v>235</v>
       </c>
-      <c r="B517" s="0">
-        <v>3</v>
+      <c r="B517" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C517" s="0" t="s">
-        <v>1</v>
+        <v>406</v>
       </c>
       <c r="D517" s="0" t="s">
         <v>237</v>
@@ -9568,11 +10069,11 @@
       <c r="A518" s="0" t="s">
         <v>235</v>
       </c>
-      <c r="B518" s="0">
-        <v>3</v>
+      <c r="B518" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C518" s="0" t="s">
-        <v>1</v>
+        <v>406</v>
       </c>
       <c r="D518" s="0" t="s">
         <v>237</v>
@@ -9585,11 +10086,11 @@
       <c r="A519" s="0" t="s">
         <v>235</v>
       </c>
-      <c r="B519" s="0">
-        <v>3</v>
+      <c r="B519" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C519" s="0" t="s">
-        <v>1</v>
+        <v>406</v>
       </c>
       <c r="D519" s="0" t="s">
         <v>237</v>
@@ -9602,11 +10103,11 @@
       <c r="A520" s="0" t="s">
         <v>235</v>
       </c>
-      <c r="B520" s="0">
-        <v>3</v>
+      <c r="B520" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="C520" s="0" t="s">
-        <v>1</v>
+        <v>406</v>
       </c>
       <c r="D520" s="0" t="s">
         <v>237</v>
@@ -9619,11 +10120,11 @@
       <c r="A521" s="0" t="s">
         <v>235</v>
       </c>
-      <c r="B521" s="0">
-        <v>4</v>
+      <c r="B521" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C521" s="0" t="s">
-        <v>1</v>
+        <v>407</v>
       </c>
       <c r="D521" s="0" t="s">
         <v>237</v>
@@ -9636,11 +10137,11 @@
       <c r="A522" s="0" t="s">
         <v>235</v>
       </c>
-      <c r="B522" s="0">
-        <v>4</v>
+      <c r="B522" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C522" s="0" t="s">
-        <v>1</v>
+        <v>407</v>
       </c>
       <c r="D522" s="0" t="s">
         <v>237</v>
@@ -9653,11 +10154,11 @@
       <c r="A523" s="0" t="s">
         <v>235</v>
       </c>
-      <c r="B523" s="0">
-        <v>4</v>
+      <c r="B523" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C523" s="0" t="s">
-        <v>1</v>
+        <v>407</v>
       </c>
       <c r="D523" s="0" t="s">
         <v>237</v>
@@ -9670,11 +10171,11 @@
       <c r="A524" s="0" t="s">
         <v>235</v>
       </c>
-      <c r="B524" s="0">
-        <v>4</v>
+      <c r="B524" s="0" t="s">
+        <v>250</v>
       </c>
       <c r="C524" s="0" t="s">
-        <v>1</v>
+        <v>407</v>
       </c>
       <c r="D524" s="0" t="s">
         <v>237</v>
